--- a/www/flightdata/xlsx/eoss-400.xlsx
+++ b/www/flightdata/xlsx/eoss-400.xlsx
@@ -5367,7 +5367,7 @@
         <v>46144.32238730324</v>
       </c>
       <c r="D2" s="1">
-        <v>46144.57232638889</v>
+        <v>46144.32232638889</v>
       </c>
       <c r="E2">
         <v>5206</v>
@@ -5474,7 +5474,7 @@
         <v>46144.32258954861</v>
       </c>
       <c r="D3" s="1">
-        <v>46144.57256944444</v>
+        <v>46144.32256944444</v>
       </c>
       <c r="E3">
         <v>5640</v>
@@ -5605,7 +5605,7 @@
         <v>46144.32270273148</v>
       </c>
       <c r="D4" s="1">
-        <v>46144.57267361111</v>
+        <v>46144.32267361111</v>
       </c>
       <c r="E4">
         <v>5815</v>
@@ -5748,7 +5748,7 @@
         <v>46144.32281790509</v>
       </c>
       <c r="D5" s="1">
-        <v>46144.572800925926</v>
+        <v>46144.322800925926</v>
       </c>
       <c r="E5">
         <v>6038</v>
@@ -5870,7 +5870,7 @@
         <v>46144.32293704861</v>
       </c>
       <c r="D6" s="1">
-        <v>46144.572916666664</v>
+        <v>46144.322916666664</v>
       </c>
       <c r="E6">
         <v>6342</v>
@@ -6013,7 +6013,7 @@
         <v>46144.323078622685</v>
       </c>
       <c r="D7" s="1">
-        <v>46144.57302083333</v>
+        <v>46144.32302083333</v>
       </c>
       <c r="E7">
         <v>6513</v>
@@ -6156,7 +6156,7 @@
         <v>46144.32316517361</v>
       </c>
       <c r="D8" s="1">
-        <v>46144.57314814815</v>
+        <v>46144.32314814815</v>
       </c>
       <c r="E8">
         <v>6710</v>
@@ -6278,7 +6278,7 @@
         <v>46144.32328409722</v>
       </c>
       <c r="D9" s="1">
-        <v>46144.57326388889</v>
+        <v>46144.32326388889</v>
       </c>
       <c r="E9">
         <v>7031</v>
@@ -6421,7 +6421,7 @@
         <v>46144.32339752315</v>
       </c>
       <c r="D10" s="1">
-        <v>46144.57336805556</v>
+        <v>46144.32336805556</v>
       </c>
       <c r="E10">
         <v>7186</v>
@@ -6564,7 +6564,7 @@
         <v>46144.32351322917</v>
       </c>
       <c r="D11" s="1">
-        <v>46144.57349537037</v>
+        <v>46144.32349537037</v>
       </c>
       <c r="E11">
         <v>7380</v>
@@ -6686,7 +6686,7 @@
         <v>46144.323631493055</v>
       </c>
       <c r="D12" s="1">
-        <v>46144.57361111111</v>
+        <v>46144.32361111111</v>
       </c>
       <c r="E12">
         <v>7691</v>
@@ -6829,7 +6829,7 @@
         <v>46144.323773564814</v>
       </c>
       <c r="D13" s="1">
-        <v>46144.57371527778</v>
+        <v>46144.32371527778</v>
       </c>
       <c r="E13">
         <v>7847</v>
@@ -6972,7 +6972,7 @@
         <v>46144.32385987268</v>
       </c>
       <c r="D14" s="1">
-        <v>46144.573842592596</v>
+        <v>46144.323842592596</v>
       </c>
       <c r="E14">
         <v>8065</v>
@@ -7094,7 +7094,7 @@
         <v>46144.3239791088</v>
       </c>
       <c r="D15" s="1">
-        <v>46144.573958333334</v>
+        <v>46144.323958333334</v>
       </c>
       <c r="E15">
         <v>8410</v>
@@ -7237,7 +7237,7 @@
         <v>46144.324091759256</v>
       </c>
       <c r="D16" s="1">
-        <v>46144.5740625</v>
+        <v>46144.3240625</v>
       </c>
       <c r="E16">
         <v>8549</v>
@@ -7380,7 +7380,7 @@
         <v>46144.32420795139</v>
       </c>
       <c r="D17" s="1">
-        <v>46144.57418981481</v>
+        <v>46144.32418981481</v>
       </c>
       <c r="E17">
         <v>8754</v>
@@ -7502,7 +7502,7 @@
         <v>46144.3243265162</v>
       </c>
       <c r="D18" s="1">
-        <v>46144.57430555556</v>
+        <v>46144.32430555556</v>
       </c>
       <c r="E18">
         <v>9065</v>
@@ -7645,7 +7645,7 @@
         <v>46144.324467453705</v>
       </c>
       <c r="D19" s="1">
-        <v>46144.57440972222</v>
+        <v>46144.32440972222</v>
       </c>
       <c r="E19">
         <v>9245</v>
@@ -7788,7 +7788,7 @@
         <v>46144.324555046296</v>
       </c>
       <c r="D20" s="1">
-        <v>46144.574537037035</v>
+        <v>46144.324537037035</v>
       </c>
       <c r="E20">
         <v>9450</v>
@@ -7910,7 +7910,7 @@
         <v>46144.32467311343</v>
       </c>
       <c r="D21" s="1">
-        <v>46144.57465277778</v>
+        <v>46144.32465277778</v>
       </c>
       <c r="E21">
         <v>9761</v>
@@ -8053,7 +8053,7 @@
         <v>46144.32478577546</v>
       </c>
       <c r="D22" s="1">
-        <v>46144.57475694444</v>
+        <v>46144.32475694444</v>
       </c>
       <c r="E22">
         <v>9939</v>
@@ -8196,7 +8196,7 @@
         <v>46144.32490181713</v>
       </c>
       <c r="D23" s="1">
-        <v>46144.57488425926</v>
+        <v>46144.32488425926</v>
       </c>
       <c r="E23">
         <v>10155</v>
@@ -8318,7 +8318,7 @@
         <v>46144.32502038195</v>
       </c>
       <c r="D24" s="1">
-        <v>46144.575</v>
+        <v>46144.325</v>
       </c>
       <c r="E24">
         <v>10474</v>
@@ -8461,7 +8461,7 @@
         <v>46144.32516179398</v>
       </c>
       <c r="D25" s="1">
-        <v>46144.575104166666</v>
+        <v>46144.325104166666</v>
       </c>
       <c r="E25">
         <v>10650</v>
@@ -8604,7 +8604,7 @@
         <v>46144.325250787035</v>
       </c>
       <c r="D26" s="1">
-        <v>46144.57523148148</v>
+        <v>46144.32523148148</v>
       </c>
       <c r="E26">
         <v>10854</v>
@@ -8726,7 +8726,7 @@
         <v>46144.32536829861</v>
       </c>
       <c r="D27" s="1">
-        <v>46144.57534722222</v>
+        <v>46144.32534722222</v>
       </c>
       <c r="E27">
         <v>11184</v>
@@ -8869,7 +8869,7 @@
         <v>46144.3254809375</v>
       </c>
       <c r="D28" s="1">
-        <v>46144.57545138889</v>
+        <v>46144.32545138889</v>
       </c>
       <c r="E28">
         <v>11359</v>
@@ -9012,7 +9012,7 @@
         <v>46144.32559662037</v>
       </c>
       <c r="D29" s="1">
-        <v>46144.575578703705</v>
+        <v>46144.325578703705</v>
       </c>
       <c r="E29">
         <v>11560</v>
@@ -9134,7 +9134,7 @@
         <v>46144.32571471065</v>
       </c>
       <c r="D30" s="1">
-        <v>46144.575694444444</v>
+        <v>46144.325694444444</v>
       </c>
       <c r="E30">
         <v>11888</v>
@@ -9277,7 +9277,7 @@
         <v>46144.325857083335</v>
       </c>
       <c r="D31" s="1">
-        <v>46144.57579861111</v>
+        <v>46144.32579861111</v>
       </c>
       <c r="E31">
         <v>12070</v>
@@ -9420,7 +9420,7 @@
         <v>46144.32594434028</v>
       </c>
       <c r="D32" s="1">
-        <v>46144.57592592593</v>
+        <v>46144.32592592593</v>
       </c>
       <c r="E32">
         <v>12269</v>
@@ -9542,7 +9542,7 @@
         <v>46144.32606277778</v>
       </c>
       <c r="D33" s="1">
-        <v>46144.57604166667</v>
+        <v>46144.32604166667</v>
       </c>
       <c r="E33">
         <v>12586</v>
@@ -9685,7 +9685,7 @@
         <v>46144.32617486111</v>
       </c>
       <c r="D34" s="1">
-        <v>46144.576145833336</v>
+        <v>46144.326145833336</v>
       </c>
       <c r="E34">
         <v>12778</v>
@@ -9828,7 +9828,7 @@
         <v>46144.32629135417</v>
       </c>
       <c r="D35" s="1">
-        <v>46144.576273148145</v>
+        <v>46144.326273148145</v>
       </c>
       <c r="E35">
         <v>12990</v>
@@ -9950,7 +9950,7 @@
         <v>46144.326408981484</v>
       </c>
       <c r="D36" s="1">
-        <v>46144.57638888889</v>
+        <v>46144.32638888889</v>
       </c>
       <c r="E36">
         <v>13318</v>
@@ -10093,7 +10093,7 @@
         <v>46144.32655215278</v>
       </c>
       <c r="D37" s="1">
-        <v>46144.57649305555</v>
+        <v>46144.32649305555</v>
       </c>
       <c r="E37">
         <v>13511</v>
@@ -10236,7 +10236,7 @@
         <v>46144.32663778935</v>
       </c>
       <c r="D38" s="1">
-        <v>46144.57662037037</v>
+        <v>46144.32662037037</v>
       </c>
       <c r="E38">
         <v>13725</v>
@@ -10358,7 +10358,7 @@
         <v>46144.32675684028</v>
       </c>
       <c r="D39" s="1">
-        <v>46144.576736111114</v>
+        <v>46144.326736111114</v>
       </c>
       <c r="E39">
         <v>14064</v>
@@ -10501,7 +10501,7 @@
         <v>46144.32686916667</v>
       </c>
       <c r="D40" s="1">
-        <v>46144.576840277776</v>
+        <v>46144.326840277776</v>
       </c>
       <c r="E40">
         <v>14252</v>
@@ -10644,7 +10644,7 @@
         <v>46144.326985023145</v>
       </c>
       <c r="D41" s="1">
-        <v>46144.57696759259</v>
+        <v>46144.32696759259</v>
       </c>
       <c r="E41">
         <v>14477</v>
@@ -10766,7 +10766,7 @@
         <v>46144.32710398148</v>
       </c>
       <c r="D42" s="1">
-        <v>46144.57708333333</v>
+        <v>46144.32708333333</v>
       </c>
       <c r="E42">
         <v>14814</v>
@@ -10909,7 +10909,7 @@
         <v>46144.3272453125</v>
       </c>
       <c r="D43" s="1">
-        <v>46144.5771875</v>
+        <v>46144.3271875</v>
       </c>
       <c r="E43">
         <v>15012</v>
@@ -11052,7 +11052,7 @@
         <v>46144.32733414352</v>
       </c>
       <c r="D44" s="1">
-        <v>46144.577314814815</v>
+        <v>46144.327314814815</v>
       </c>
       <c r="E44">
         <v>15238</v>
@@ -11174,7 +11174,7 @@
         <v>46144.327451481484</v>
       </c>
       <c r="D45" s="1">
-        <v>46144.57743055555</v>
+        <v>46144.32743055555</v>
       </c>
       <c r="E45">
         <v>15580</v>
@@ -11317,7 +11317,7 @@
         <v>46144.32756415509</v>
       </c>
       <c r="D46" s="1">
-        <v>46144.57753472222</v>
+        <v>46144.32753472222</v>
       </c>
       <c r="E46">
         <v>15782</v>
@@ -11460,7 +11460,7 @@
         <v>46144.32767974537</v>
       </c>
       <c r="D47" s="1">
-        <v>46144.57766203704</v>
+        <v>46144.32766203704</v>
       </c>
       <c r="E47">
         <v>16006</v>
@@ -11582,7 +11582,7 @@
         <v>46144.32779821759</v>
       </c>
       <c r="D48" s="1">
-        <v>46144.57777777778</v>
+        <v>46144.32777777778</v>
       </c>
       <c r="E48">
         <v>16348</v>
@@ -11725,7 +11725,7 @@
         <v>46144.32793966435</v>
       </c>
       <c r="D49" s="1">
-        <v>46144.577881944446</v>
+        <v>46144.327881944446</v>
       </c>
       <c r="E49">
         <v>16552</v>
@@ -11868,7 +11868,7 @@
         <v>46144.32802649306</v>
       </c>
       <c r="D50" s="1">
-        <v>46144.57800925926</v>
+        <v>46144.32800925926</v>
       </c>
       <c r="E50">
         <v>16784</v>
@@ -11990,7 +11990,7 @@
         <v>46144.32814575231</v>
       </c>
       <c r="D51" s="1">
-        <v>46144.578125</v>
+        <v>46144.328125</v>
       </c>
       <c r="E51">
         <v>17151</v>
@@ -12133,7 +12133,7 @@
         <v>46144.328257789355</v>
       </c>
       <c r="D52" s="1">
-        <v>46144.57822916667</v>
+        <v>46144.32822916667</v>
       </c>
       <c r="E52">
         <v>17340</v>
@@ -12276,7 +12276,7 @@
         <v>46144.32837488426</v>
       </c>
       <c r="D53" s="1">
-        <v>46144.578356481485</v>
+        <v>46144.328356481485</v>
       </c>
       <c r="E53">
         <v>17565</v>
@@ -12398,7 +12398,7 @@
         <v>46144.32849270834</v>
       </c>
       <c r="D54" s="1">
-        <v>46144.57847222222</v>
+        <v>46144.32847222222</v>
       </c>
       <c r="E54">
         <v>17907</v>
@@ -12541,7 +12541,7 @@
         <v>46144.32863469907</v>
       </c>
       <c r="D55" s="1">
-        <v>46144.578576388885</v>
+        <v>46144.328576388885</v>
       </c>
       <c r="E55">
         <v>18105</v>
@@ -12684,7 +12684,7 @@
         <v>46144.328724293984</v>
       </c>
       <c r="D56" s="1">
-        <v>46144.5787037037</v>
+        <v>46144.3287037037</v>
       </c>
       <c r="E56">
         <v>18336</v>
@@ -12806,7 +12806,7 @@
         <v>46144.32884068287</v>
       </c>
       <c r="D57" s="1">
-        <v>46144.57881944445</v>
+        <v>46144.32881944445</v>
       </c>
       <c r="E57">
         <v>18685</v>
@@ -12949,7 +12949,7 @@
         <v>46144.32895303241</v>
       </c>
       <c r="D58" s="1">
-        <v>46144.57892361111</v>
+        <v>46144.32892361111</v>
       </c>
       <c r="E58">
         <v>18898</v>
@@ -13092,7 +13092,7 @@
         <v>46144.329068831015</v>
       </c>
       <c r="D59" s="1">
-        <v>46144.579050925924</v>
+        <v>46144.329050925924</v>
       </c>
       <c r="E59">
         <v>19123</v>
@@ -13214,7 +13214,7 @@
         <v>46144.32918724537</v>
       </c>
       <c r="D60" s="1">
-        <v>46144.57916666667</v>
+        <v>46144.32916666667</v>
       </c>
       <c r="E60">
         <v>19494</v>
@@ -13357,7 +13357,7 @@
         <v>46144.329329375</v>
       </c>
       <c r="D61" s="1">
-        <v>46144.57927083333</v>
+        <v>46144.32927083333</v>
       </c>
       <c r="E61">
         <v>19693</v>
@@ -13500,7 +13500,7 @@
         <v>46144.32941695602</v>
       </c>
       <c r="D62" s="1">
-        <v>46144.57939814815</v>
+        <v>46144.32939814815</v>
       </c>
       <c r="E62">
         <v>19934</v>
@@ -13622,7 +13622,7 @@
         <v>46144.329534675926</v>
       </c>
       <c r="D63" s="1">
-        <v>46144.579513888886</v>
+        <v>46144.329513888886</v>
       </c>
       <c r="E63">
         <v>20268</v>
@@ -13765,7 +13765,7 @@
         <v>46144.32964793981</v>
       </c>
       <c r="D64" s="1">
-        <v>46144.579618055555</v>
+        <v>46144.329618055555</v>
       </c>
       <c r="E64">
         <v>20481</v>
@@ -13908,7 +13908,7 @@
         <v>46144.32976284722</v>
       </c>
       <c r="D65" s="1">
-        <v>46144.57974537037</v>
+        <v>46144.32974537037</v>
       </c>
       <c r="E65">
         <v>20731</v>
@@ -14030,7 +14030,7 @@
         <v>46144.32988193287</v>
       </c>
       <c r="D66" s="1">
-        <v>46144.57986111111</v>
+        <v>46144.32986111111</v>
       </c>
       <c r="E66">
         <v>21088</v>
@@ -14173,7 +14173,7 @@
         <v>46144.33002412037</v>
       </c>
       <c r="D67" s="1">
-        <v>46144.57996527778</v>
+        <v>46144.32996527778</v>
       </c>
       <c r="E67">
         <v>21306</v>
@@ -14316,7 +14316,7 @@
         <v>46144.33011097222</v>
       </c>
       <c r="D68" s="1">
-        <v>46144.580092592594</v>
+        <v>46144.330092592594</v>
       </c>
       <c r="E68">
         <v>21541</v>
@@ -14438,7 +14438,7 @@
         <v>46144.330228217594</v>
       </c>
       <c r="D69" s="1">
-        <v>46144.58020833333</v>
+        <v>46144.33020833333</v>
       </c>
       <c r="E69">
         <v>21896</v>
@@ -14581,7 +14581,7 @@
         <v>46144.330341782406</v>
       </c>
       <c r="D70" s="1">
-        <v>46144.5803125</v>
+        <v>46144.3303125</v>
       </c>
       <c r="E70">
         <v>22130</v>
@@ -14724,7 +14724,7 @@
         <v>46144.3304575463</v>
       </c>
       <c r="D71" s="1">
-        <v>46144.58043981482</v>
+        <v>46144.33043981482</v>
       </c>
       <c r="E71">
         <v>22362</v>
@@ -14846,7 +14846,7 @@
         <v>46144.330576238426</v>
       </c>
       <c r="D72" s="1">
-        <v>46144.580555555556</v>
+        <v>46144.330555555556</v>
       </c>
       <c r="E72">
         <v>22720</v>
@@ -14989,7 +14989,7 @@
         <v>46144.33071894676</v>
       </c>
       <c r="D73" s="1">
-        <v>46144.580659722225</v>
+        <v>46144.330659722225</v>
       </c>
       <c r="E73">
         <v>22933</v>
@@ -15132,7 +15132,7 @@
         <v>46144.33080538194</v>
       </c>
       <c r="D74" s="1">
-        <v>46144.58078703703</v>
+        <v>46144.33078703703</v>
       </c>
       <c r="E74">
         <v>23179</v>
@@ -15254,7 +15254,7 @@
         <v>46144.33092364583</v>
       </c>
       <c r="D75" s="1">
-        <v>46144.58090277778</v>
+        <v>46144.33090277778</v>
       </c>
       <c r="E75">
         <v>23541</v>
@@ -15397,7 +15397,7 @@
         <v>46144.33103609954</v>
       </c>
       <c r="D76" s="1">
-        <v>46144.58100694444</v>
+        <v>46144.33100694444</v>
       </c>
       <c r="E76">
         <v>23757</v>
@@ -15540,7 +15540,7 @@
         <v>46144.33115150463</v>
       </c>
       <c r="D77" s="1">
-        <v>46144.58113425926</v>
+        <v>46144.33113425926</v>
       </c>
       <c r="E77">
         <v>24006</v>
@@ -15662,7 +15662,7 @@
         <v>46144.33127019676</v>
       </c>
       <c r="D78" s="1">
-        <v>46144.58125</v>
+        <v>46144.33125</v>
       </c>
       <c r="E78">
         <v>24350</v>
@@ -15805,7 +15805,7 @@
         <v>46144.33141252315</v>
       </c>
       <c r="D79" s="1">
-        <v>46144.581354166665</v>
+        <v>46144.331354166665</v>
       </c>
       <c r="E79">
         <v>24547</v>
@@ -15948,7 +15948,7 @@
         <v>46144.33161769676</v>
       </c>
       <c r="D80" s="1">
-        <v>46144.58159722222</v>
+        <v>46144.33159722222</v>
       </c>
       <c r="E80">
         <v>25135</v>
@@ -16091,7 +16091,7 @@
         <v>46144.331730868056</v>
       </c>
       <c r="D81" s="1">
-        <v>46144.58170138889</v>
+        <v>46144.33170138889</v>
       </c>
       <c r="E81">
         <v>25335</v>
@@ -16234,7 +16234,7 @@
         <v>46144.33196506945</v>
       </c>
       <c r="D82" s="1">
-        <v>46144.58194444444</v>
+        <v>46144.33194444444</v>
       </c>
       <c r="E82">
         <v>25924</v>
@@ -16377,7 +16377,7 @@
         <v>46144.33210762731</v>
       </c>
       <c r="D83" s="1">
-        <v>46144.58204861111</v>
+        <v>46144.33204861111</v>
       </c>
       <c r="E83">
         <v>26141</v>
@@ -16520,7 +16520,7 @@
         <v>46144.332192835645</v>
       </c>
       <c r="D84" s="1">
-        <v>46144.58217592593</v>
+        <v>46144.33217592593</v>
       </c>
       <c r="E84">
         <v>26375</v>
@@ -16642,7 +16642,7 @@
         <v>46144.33231194445</v>
       </c>
       <c r="D85" s="1">
-        <v>46144.582291666666</v>
+        <v>46144.332291666666</v>
       </c>
       <c r="E85">
         <v>26734</v>
@@ -16785,7 +16785,7 @@
         <v>46144.33242467593</v>
       </c>
       <c r="D86" s="1">
-        <v>46144.582395833335</v>
+        <v>46144.332395833335</v>
       </c>
       <c r="E86">
         <v>26943</v>
@@ -16928,7 +16928,7 @@
         <v>46144.33254018518</v>
       </c>
       <c r="D87" s="1">
-        <v>46144.58252314815</v>
+        <v>46144.33252314815</v>
       </c>
       <c r="E87">
         <v>27165</v>
@@ -17050,7 +17050,7 @@
         <v>46144.33265949074</v>
       </c>
       <c r="D88" s="1">
-        <v>46144.58263888889</v>
+        <v>46144.33263888889</v>
       </c>
       <c r="E88">
         <v>27518</v>
@@ -17193,7 +17193,7 @@
         <v>46144.332801909724</v>
       </c>
       <c r="D89" s="1">
-        <v>46144.58274305556</v>
+        <v>46144.33274305556</v>
       </c>
       <c r="E89">
         <v>27730</v>
@@ -17336,7 +17336,7 @@
         <v>46144.33288835648</v>
       </c>
       <c r="D90" s="1">
-        <v>46144.582870370374</v>
+        <v>46144.332870370374</v>
       </c>
       <c r="E90">
         <v>27963</v>
@@ -17458,7 +17458,7 @@
         <v>46144.333006388886</v>
       </c>
       <c r="D91" s="1">
-        <v>46144.58298611111</v>
+        <v>46144.33298611111</v>
       </c>
       <c r="E91">
         <v>28311</v>
@@ -17601,7 +17601,7 @@
         <v>46144.33312019676</v>
       </c>
       <c r="D92" s="1">
-        <v>46144.583090277774</v>
+        <v>46144.333090277774</v>
       </c>
       <c r="E92">
         <v>28507</v>
@@ -17744,7 +17744,7 @@
         <v>46144.33323681713</v>
       </c>
       <c r="D93" s="1">
-        <v>46144.58321759259</v>
+        <v>46144.33321759259</v>
       </c>
       <c r="E93">
         <v>28727</v>
@@ -17866,7 +17866,7 @@
         <v>46144.333353449074</v>
       </c>
       <c r="D94" s="1">
-        <v>46144.583333333336</v>
+        <v>46144.333333333336</v>
       </c>
       <c r="E94">
         <v>29052</v>
@@ -18009,7 +18009,7 @@
         <v>46144.33349599537</v>
       </c>
       <c r="D95" s="1">
-        <v>46144.5834375</v>
+        <v>46144.3334375</v>
       </c>
       <c r="E95">
         <v>29245</v>
@@ -18152,7 +18152,7 @@
         <v>46144.33358244213</v>
       </c>
       <c r="D96" s="1">
-        <v>46144.58356481481</v>
+        <v>46144.33356481481</v>
       </c>
       <c r="E96">
         <v>29462</v>
@@ -18274,7 +18274,7 @@
         <v>46144.33370081019</v>
       </c>
       <c r="D97" s="1">
-        <v>46144.58368055556</v>
+        <v>46144.33368055556</v>
       </c>
       <c r="E97">
         <v>29787</v>
@@ -18417,7 +18417,7 @@
         <v>46144.33381430556</v>
       </c>
       <c r="D98" s="1">
-        <v>46144.58378472222</v>
+        <v>46144.33378472222</v>
       </c>
       <c r="E98">
         <v>29971</v>
@@ -18560,7 +18560,7 @@
         <v>46144.33404756944</v>
       </c>
       <c r="D99" s="1">
-        <v>46144.584027777775</v>
+        <v>46144.334027777775</v>
       </c>
       <c r="E99">
         <v>30538</v>
@@ -18703,7 +18703,7 @@
         <v>46144.3341909375</v>
       </c>
       <c r="D100" s="1">
-        <v>46144.584131944444</v>
+        <v>46144.334131944444</v>
       </c>
       <c r="E100">
         <v>30733</v>
@@ -18846,7 +18846,7 @@
         <v>46144.334278298615</v>
       </c>
       <c r="D101" s="1">
-        <v>46144.58425925926</v>
+        <v>46144.33425925926</v>
       </c>
       <c r="E101">
         <v>30949</v>
@@ -18968,7 +18968,7 @@
         <v>46144.33439521991</v>
       </c>
       <c r="D102" s="1">
-        <v>46144.584375</v>
+        <v>46144.334375</v>
       </c>
       <c r="E102">
         <v>31272</v>
@@ -19111,7 +19111,7 @@
         <v>46144.33450896991</v>
       </c>
       <c r="D103" s="1">
-        <v>46144.58447916667</v>
+        <v>46144.33447916667</v>
       </c>
       <c r="E103">
         <v>31444</v>
@@ -19254,7 +19254,7 @@
         <v>46144.334624710646</v>
       </c>
       <c r="D104" s="1">
-        <v>46144.58460648148</v>
+        <v>46144.33460648148</v>
       </c>
       <c r="E104">
         <v>31680</v>
@@ -19376,7 +19376,7 @@
         <v>46144.3347418287</v>
       </c>
       <c r="D105" s="1">
-        <v>46144.58472222222</v>
+        <v>46144.33472222222</v>
       </c>
       <c r="E105">
         <v>32005</v>
@@ -19519,7 +19519,7 @@
         <v>46144.33488512731</v>
       </c>
       <c r="D106" s="1">
-        <v>46144.58482638889</v>
+        <v>46144.33482638889</v>
       </c>
       <c r="E106">
         <v>32174</v>
@@ -19662,7 +19662,7 @@
         <v>46144.334972094905</v>
       </c>
       <c r="D107" s="1">
-        <v>46144.58495370371</v>
+        <v>46144.33495370371</v>
       </c>
       <c r="E107">
         <v>32386</v>
@@ -19784,7 +19784,7 @@
         <v>46144.33509032407</v>
       </c>
       <c r="D108" s="1">
-        <v>46144.585069444445</v>
+        <v>46144.335069444445</v>
       </c>
       <c r="E108">
         <v>32743</v>
@@ -19927,7 +19927,7 @@
         <v>46144.33520306713</v>
       </c>
       <c r="D109" s="1">
-        <v>46144.585173611114</v>
+        <v>46144.335173611114</v>
       </c>
       <c r="E109">
         <v>32896</v>
@@ -20070,7 +20070,7 @@
         <v>46144.33531861111</v>
       </c>
       <c r="D110" s="1">
-        <v>46144.58530092592</v>
+        <v>46144.33530092592</v>
       </c>
       <c r="E110">
         <v>33131</v>
@@ -20192,7 +20192,7 @@
         <v>46144.3354371875</v>
       </c>
       <c r="D111" s="1">
-        <v>46144.58541666667</v>
+        <v>46144.33541666667</v>
       </c>
       <c r="E111">
         <v>33457</v>
@@ -20335,7 +20335,7 @@
         <v>46144.33557983796</v>
       </c>
       <c r="D112" s="1">
-        <v>46144.58552083333</v>
+        <v>46144.33552083333</v>
       </c>
       <c r="E112">
         <v>33621</v>
@@ -20478,7 +20478,7 @@
         <v>46144.335665300925</v>
       </c>
       <c r="D113" s="1">
-        <v>46144.585648148146</v>
+        <v>46144.335648148146</v>
       </c>
       <c r="E113">
         <v>33826</v>
@@ -20600,7 +20600,7 @@
         <v>46144.33578393519</v>
       </c>
       <c r="D114" s="1">
-        <v>46144.58576388889</v>
+        <v>46144.33576388889</v>
       </c>
       <c r="E114">
         <v>34134</v>
@@ -20743,7 +20743,7 @@
         <v>46144.33589771991</v>
       </c>
       <c r="D115" s="1">
-        <v>46144.585868055554</v>
+        <v>46144.335868055554</v>
       </c>
       <c r="E115">
         <v>34325</v>
@@ -20886,7 +20886,7 @@
         <v>46144.33601240741</v>
       </c>
       <c r="D116" s="1">
-        <v>46144.58599537037</v>
+        <v>46144.33599537037</v>
       </c>
       <c r="E116">
         <v>34548</v>
@@ -21008,7 +21008,7 @@
         <v>46144.33613179398</v>
       </c>
       <c r="D117" s="1">
-        <v>46144.58611111111</v>
+        <v>46144.33611111111</v>
       </c>
       <c r="E117">
         <v>34876</v>
@@ -21151,7 +21151,7 @@
         <v>46144.336274305555</v>
       </c>
       <c r="D118" s="1">
-        <v>46144.58621527778</v>
+        <v>46144.33621527778</v>
       </c>
       <c r="E118">
         <v>35080</v>
@@ -21294,7 +21294,7 @@
         <v>46144.33647841435</v>
       </c>
       <c r="D119" s="1">
-        <v>46144.58645833333</v>
+        <v>46144.33645833333</v>
       </c>
       <c r="E119">
         <v>35606</v>
@@ -21437,7 +21437,7 @@
         <v>46144.33659248843</v>
       </c>
       <c r="D120" s="1">
-        <v>46144.5865625</v>
+        <v>46144.3365625</v>
       </c>
       <c r="E120">
         <v>35783</v>
@@ -21580,7 +21580,7 @@
         <v>46144.3367074537</v>
       </c>
       <c r="D121" s="1">
-        <v>46144.586689814816</v>
+        <v>46144.336689814816</v>
       </c>
       <c r="E121">
         <v>36008</v>
@@ -21702,7 +21702,7 @@
         <v>46144.33682611111</v>
       </c>
       <c r="D122" s="1">
-        <v>46144.586805555555</v>
+        <v>46144.336805555555</v>
       </c>
       <c r="E122">
         <v>36336</v>
@@ -21845,7 +21845,7 @@
         <v>46144.33696842592</v>
       </c>
       <c r="D123" s="1">
-        <v>46144.586909722224</v>
+        <v>46144.336909722224</v>
       </c>
       <c r="E123">
         <v>36525</v>
@@ -21988,7 +21988,7 @@
         <v>46144.33705443287</v>
       </c>
       <c r="D124" s="1">
-        <v>46144.58703703704</v>
+        <v>46144.33703703704</v>
       </c>
       <c r="E124">
         <v>36730</v>
@@ -22110,7 +22110,7 @@
         <v>46144.337173391206</v>
       </c>
       <c r="D125" s="1">
-        <v>46144.58715277778</v>
+        <v>46144.33715277778</v>
       </c>
       <c r="E125">
         <v>37133</v>
@@ -22253,7 +22253,7 @@
         <v>46144.33728717593</v>
       </c>
       <c r="D126" s="1">
-        <v>46144.58725694445</v>
+        <v>46144.33725694445</v>
       </c>
       <c r="E126">
         <v>37246</v>
@@ -22396,7 +22396,7 @@
         <v>46144.33740263889</v>
       </c>
       <c r="D127" s="1">
-        <v>46144.58738425926</v>
+        <v>46144.33738425926</v>
       </c>
       <c r="E127">
         <v>37416</v>
@@ -22518,7 +22518,7 @@
         <v>46144.3375203125</v>
       </c>
       <c r="D128" s="1">
-        <v>46144.5875</v>
+        <v>46144.3375</v>
       </c>
       <c r="E128">
         <v>37735</v>
@@ -22661,7 +22661,7 @@
         <v>46144.33766341435</v>
       </c>
       <c r="D129" s="1">
-        <v>46144.58760416666</v>
+        <v>46144.33760416666</v>
       </c>
       <c r="E129">
         <v>37936</v>
@@ -22804,7 +22804,7 @@
         <v>46144.33798167824</v>
       </c>
       <c r="D130" s="1">
-        <v>46144.58795138889</v>
+        <v>46144.33795138889</v>
       </c>
       <c r="E130">
         <v>38535</v>
@@ -22947,7 +22947,7 @@
         <v>46144.33809690972</v>
       </c>
       <c r="D131" s="1">
-        <v>46144.5880787037</v>
+        <v>46144.3380787037</v>
       </c>
       <c r="E131">
         <v>38702</v>
@@ -23069,7 +23069,7 @@
         <v>46144.33821508102</v>
       </c>
       <c r="D132" s="1">
-        <v>46144.58819444444</v>
+        <v>46144.33819444444</v>
       </c>
       <c r="E132">
         <v>39056</v>
@@ -23212,7 +23212,7 @@
         <v>46144.33835788194</v>
       </c>
       <c r="D133" s="1">
-        <v>46144.58829861111</v>
+        <v>46144.33829861111</v>
       </c>
       <c r="E133">
         <v>39199</v>
@@ -23355,7 +23355,7 @@
         <v>46144.33856195602</v>
       </c>
       <c r="D134" s="1">
-        <v>46144.588541666664</v>
+        <v>46144.338541666664</v>
       </c>
       <c r="E134">
         <v>39747</v>
@@ -23498,7 +23498,7 @@
         <v>46144.33867575231</v>
       </c>
       <c r="D135" s="1">
-        <v>46144.58864583333</v>
+        <v>46144.33864583333</v>
       </c>
       <c r="E135">
         <v>39877</v>
@@ -23641,7 +23641,7 @@
         <v>46144.33879149306</v>
       </c>
       <c r="D136" s="1">
-        <v>46144.58877314815</v>
+        <v>46144.33877314815</v>
       </c>
       <c r="E136">
         <v>40163</v>
@@ -23763,7 +23763,7 @@
         <v>46144.33890940972</v>
       </c>
       <c r="D137" s="1">
-        <v>46144.58888888889</v>
+        <v>46144.33888888889</v>
       </c>
       <c r="E137">
         <v>40440</v>
@@ -23906,7 +23906,7 @@
         <v>46144.339051145835</v>
       </c>
       <c r="D138" s="1">
-        <v>46144.58899305556</v>
+        <v>46144.33899305556</v>
       </c>
       <c r="E138">
         <v>40554</v>
@@ -24049,7 +24049,7 @@
         <v>46144.33913868055</v>
       </c>
       <c r="D139" s="1">
-        <v>46144.58912037037</v>
+        <v>46144.33912037037</v>
       </c>
       <c r="E139">
         <v>40806</v>
@@ -24171,7 +24171,7 @@
         <v>46144.339255914354</v>
       </c>
       <c r="D140" s="1">
-        <v>46144.58923611111</v>
+        <v>46144.33923611111</v>
       </c>
       <c r="E140">
         <v>41058</v>
@@ -24317,7 +24317,7 @@
         <v>46144.339370023146</v>
       </c>
       <c r="D141" s="1">
-        <v>46144.58934027778</v>
+        <v>46144.33934027778</v>
       </c>
       <c r="E141">
         <v>41164</v>
@@ -24460,7 +24460,7 @@
         <v>46144.33948519676</v>
       </c>
       <c r="D142" s="1">
-        <v>46144.589467592596</v>
+        <v>46144.339467592596</v>
       </c>
       <c r="E142">
         <v>41370</v>
@@ -24582,7 +24582,7 @@
         <v>46144.33960423611</v>
       </c>
       <c r="D143" s="1">
-        <v>46144.589583333334</v>
+        <v>46144.339583333334</v>
       </c>
       <c r="E143">
         <v>41623</v>
@@ -24725,7 +24725,7 @@
         <v>46144.33974675926</v>
       </c>
       <c r="D144" s="1">
-        <v>46144.5896875</v>
+        <v>46144.3396875</v>
       </c>
       <c r="E144">
         <v>41748</v>
@@ -24868,7 +24868,7 @@
         <v>46144.33983520833</v>
       </c>
       <c r="D145" s="1">
-        <v>46144.58981481481</v>
+        <v>46144.33981481481</v>
       </c>
       <c r="E145">
         <v>41964</v>
@@ -24990,7 +24990,7 @@
         <v>46144.33995150463</v>
       </c>
       <c r="D146" s="1">
-        <v>46144.58993055556</v>
+        <v>46144.33993055556</v>
       </c>
       <c r="E146">
         <v>42166</v>
@@ -25133,7 +25133,7 @@
         <v>46144.340065069446</v>
       </c>
       <c r="D147" s="1">
-        <v>46144.59003472222</v>
+        <v>46144.34003472222</v>
       </c>
       <c r="E147">
         <v>42249</v>
@@ -25276,7 +25276,7 @@
         <v>46144.34018053241</v>
       </c>
       <c r="D148" s="1">
-        <v>46144.590162037035</v>
+        <v>46144.340162037035</v>
       </c>
       <c r="E148">
         <v>42368</v>
@@ -25398,7 +25398,7 @@
         <v>46144.340298703704</v>
       </c>
       <c r="D149" s="1">
-        <v>46144.59027777778</v>
+        <v>46144.34027777778</v>
       </c>
       <c r="E149">
         <v>42603</v>
@@ -25541,7 +25541,7 @@
         <v>46144.340440844906</v>
       </c>
       <c r="D150" s="1">
-        <v>46144.59038194444</v>
+        <v>46144.34038194444</v>
       </c>
       <c r="E150">
         <v>42690</v>
@@ -25684,7 +25684,7 @@
         <v>46144.340531574075</v>
       </c>
       <c r="D151" s="1">
-        <v>46144.59050925926</v>
+        <v>46144.34050925926</v>
       </c>
       <c r="E151">
         <v>42794</v>
@@ -25806,7 +25806,7 @@
         <v>46144.34064512731</v>
       </c>
       <c r="D152" s="1">
-        <v>46144.590625</v>
+        <v>46144.340625</v>
       </c>
       <c r="E152">
         <v>42996</v>
@@ -25949,7 +25949,7 @@
         <v>46144.34075943287</v>
       </c>
       <c r="D153" s="1">
-        <v>46144.590729166666</v>
+        <v>46144.340729166666</v>
       </c>
       <c r="E153">
         <v>43084</v>
@@ -26092,7 +26092,7 @@
         <v>46144.34087564815</v>
       </c>
       <c r="D154" s="1">
-        <v>46144.59085648148</v>
+        <v>46144.34085648148</v>
       </c>
       <c r="E154">
         <v>43198</v>
@@ -26214,7 +26214,7 @@
         <v>46144.34099361111</v>
       </c>
       <c r="D155" s="1">
-        <v>46144.59097222222</v>
+        <v>46144.34097222222</v>
       </c>
       <c r="E155">
         <v>43416</v>
@@ -26357,7 +26357,7 @@
         <v>46144.34113486111</v>
       </c>
       <c r="D156" s="1">
-        <v>46144.59107638889</v>
+        <v>46144.34107638889</v>
       </c>
       <c r="E156">
         <v>43524</v>
@@ -26500,7 +26500,7 @@
         <v>46144.34122127315</v>
       </c>
       <c r="D157" s="1">
-        <v>46144.591203703705</v>
+        <v>46144.341203703705</v>
       </c>
       <c r="E157">
         <v>43746</v>
@@ -26622,7 +26622,7 @@
         <v>46144.34134009259</v>
       </c>
       <c r="D158" s="1">
-        <v>46144.591319444444</v>
+        <v>46144.341319444444</v>
       </c>
       <c r="E158">
         <v>43989</v>
@@ -26765,7 +26765,7 @@
         <v>46144.34145337963</v>
       </c>
       <c r="D159" s="1">
-        <v>46144.59142361111</v>
+        <v>46144.34142361111</v>
       </c>
       <c r="E159">
         <v>44071</v>
@@ -26908,7 +26908,7 @@
         <v>46144.34156641204</v>
       </c>
       <c r="D160" s="1">
-        <v>46144.59155092593</v>
+        <v>46144.34155092593</v>
       </c>
       <c r="E160">
         <v>44182</v>
@@ -27030,7 +27030,7 @@
         <v>46144.3416878125</v>
       </c>
       <c r="D161" s="1">
-        <v>46144.59166666667</v>
+        <v>46144.34166666667</v>
       </c>
       <c r="E161">
         <v>44401</v>
@@ -27173,7 +27173,7 @@
         <v>46144.341830081015</v>
       </c>
       <c r="D162" s="1">
-        <v>46144.591770833336</v>
+        <v>46144.341770833336</v>
       </c>
       <c r="E162">
         <v>44511</v>
@@ -27316,7 +27316,7 @@
         <v>46144.34191700231</v>
       </c>
       <c r="D163" s="1">
-        <v>46144.591898148145</v>
+        <v>46144.341898148145</v>
       </c>
       <c r="E163">
         <v>44628</v>
@@ -27438,7 +27438,7 @@
         <v>46144.34203377315</v>
       </c>
       <c r="D164" s="1">
-        <v>46144.59201388889</v>
+        <v>46144.34201388889</v>
       </c>
       <c r="E164">
         <v>44864</v>
@@ -27581,7 +27581,7 @@
         <v>46144.34214784722</v>
       </c>
       <c r="D165" s="1">
-        <v>46144.59211805555</v>
+        <v>46144.34211805555</v>
       </c>
       <c r="E165">
         <v>44953</v>
@@ -27724,7 +27724,7 @@
         <v>46144.34238136574</v>
       </c>
       <c r="D166" s="1">
-        <v>46144.592361111114</v>
+        <v>46144.342361111114</v>
       </c>
       <c r="E166">
         <v>45277</v>
@@ -27867,7 +27867,7 @@
         <v>46144.342524074076</v>
       </c>
       <c r="D167" s="1">
-        <v>46144.592465277776</v>
+        <v>46144.342465277776</v>
       </c>
       <c r="E167">
         <v>45381</v>
@@ -28010,7 +28010,7 @@
         <v>46144.34272891204</v>
       </c>
       <c r="D168" s="1">
-        <v>46144.59270833333</v>
+        <v>46144.34270833333</v>
       </c>
       <c r="E168">
         <v>45750</v>
@@ -28153,7 +28153,7 @@
         <v>46144.34284283565</v>
       </c>
       <c r="D169" s="1">
-        <v>46144.5928125</v>
+        <v>46144.3428125</v>
       </c>
       <c r="E169">
         <v>45851</v>
@@ -28296,7 +28296,7 @@
         <v>46144.34307563657</v>
       </c>
       <c r="D170" s="1">
-        <v>46144.59305555555</v>
+        <v>46144.34305555555</v>
       </c>
       <c r="E170">
         <v>46192</v>
@@ -28439,7 +28439,7 @@
         <v>46144.343219456016</v>
       </c>
       <c r="D171" s="1">
-        <v>46144.59315972222</v>
+        <v>46144.34315972222</v>
       </c>
       <c r="E171">
         <v>46292</v>
@@ -28582,7 +28582,7 @@
         <v>46144.34342321759</v>
       </c>
       <c r="D172" s="1">
-        <v>46144.59340277778</v>
+        <v>46144.34340277778</v>
       </c>
       <c r="E172">
         <v>46637</v>
@@ -28725,7 +28725,7 @@
         <v>46144.34353706019</v>
       </c>
       <c r="D173" s="1">
-        <v>46144.593506944446</v>
+        <v>46144.343506944446</v>
       </c>
       <c r="E173">
         <v>46741</v>
@@ -28868,7 +28868,7 @@
         <v>46144.34377043982</v>
       </c>
       <c r="D174" s="1">
-        <v>46144.59375</v>
+        <v>46144.34375</v>
       </c>
       <c r="E174">
         <v>47075</v>
@@ -29011,7 +29011,7 @@
         <v>46144.343913020835</v>
       </c>
       <c r="D175" s="1">
-        <v>46144.59385416667</v>
+        <v>46144.34385416667</v>
       </c>
       <c r="E175">
         <v>47162</v>
@@ -29154,7 +29154,7 @@
         <v>46144.34411824074</v>
       </c>
       <c r="D176" s="1">
-        <v>46144.59409722222</v>
+        <v>46144.34409722222</v>
       </c>
       <c r="E176">
         <v>47493</v>
@@ -29297,7 +29297,7 @@
         <v>46144.344231145835</v>
       </c>
       <c r="D177" s="1">
-        <v>46144.594201388885</v>
+        <v>46144.344201388885</v>
       </c>
       <c r="E177">
         <v>47585</v>
@@ -29440,7 +29440,7 @@
         <v>46144.344465069444</v>
       </c>
       <c r="D178" s="1">
-        <v>46144.59444444445</v>
+        <v>46144.34444444445</v>
       </c>
       <c r="E178">
         <v>47883</v>
@@ -29583,7 +29583,7 @@
         <v>46144.34460791667</v>
       </c>
       <c r="D179" s="1">
-        <v>46144.59454861111</v>
+        <v>46144.34454861111</v>
       </c>
       <c r="E179">
         <v>47963</v>
@@ -29726,7 +29726,7 @@
         <v>46144.34481126157</v>
       </c>
       <c r="D180" s="1">
-        <v>46144.59479166667</v>
+        <v>46144.34479166667</v>
       </c>
       <c r="E180">
         <v>48279</v>
@@ -29869,7 +29869,7 @@
         <v>46144.34492578704</v>
       </c>
       <c r="D181" s="1">
-        <v>46144.59489583333</v>
+        <v>46144.34489583333</v>
       </c>
       <c r="E181">
         <v>48377</v>
@@ -30012,7 +30012,7 @@
         <v>46144.34515903935</v>
       </c>
       <c r="D182" s="1">
-        <v>46144.595138888886</v>
+        <v>46144.345138888886</v>
       </c>
       <c r="E182">
         <v>48697</v>
@@ -30155,7 +30155,7 @@
         <v>46144.34530173611</v>
       </c>
       <c r="D183" s="1">
-        <v>46144.595243055555</v>
+        <v>46144.345243055555</v>
       </c>
       <c r="E183">
         <v>48773</v>
@@ -30298,7 +30298,7 @@
         <v>46144.3453868287</v>
       </c>
       <c r="D184" s="1">
-        <v>46144.59537037037</v>
+        <v>46144.34537037037</v>
       </c>
       <c r="E184">
         <v>48884</v>
@@ -30420,7 +30420,7 @@
         <v>46144.345506875</v>
       </c>
       <c r="D185" s="1">
-        <v>46144.59548611111</v>
+        <v>46144.34548611111</v>
       </c>
       <c r="E185">
         <v>49131</v>
@@ -30563,7 +30563,7 @@
         <v>46144.345624050926</v>
       </c>
       <c r="D186" s="1">
-        <v>46144.59559027778</v>
+        <v>46144.34559027778</v>
       </c>
       <c r="E186">
         <v>49232</v>
@@ -30706,7 +30706,7 @@
         <v>46144.34585365741</v>
       </c>
       <c r="D187" s="1">
-        <v>46144.59583333333</v>
+        <v>46144.34583333333</v>
       </c>
       <c r="E187">
         <v>49570</v>
@@ -30849,7 +30849,7 @@
         <v>46144.34599678241</v>
       </c>
       <c r="D188" s="1">
-        <v>46144.5959375</v>
+        <v>46144.3459375</v>
       </c>
       <c r="E188">
         <v>49671</v>
@@ -30992,7 +30992,7 @@
         <v>46144.346201099535</v>
       </c>
       <c r="D189" s="1">
-        <v>46144.596180555556</v>
+        <v>46144.346180555556</v>
       </c>
       <c r="E189">
         <v>49999</v>
@@ -31135,7 +31135,7 @@
         <v>46144.3463165162</v>
       </c>
       <c r="D190" s="1">
-        <v>46144.596284722225</v>
+        <v>46144.346284722225</v>
       </c>
       <c r="E190">
         <v>50148</v>
@@ -31278,7 +31278,7 @@
         <v>46144.346550347225</v>
       </c>
       <c r="D191" s="1">
-        <v>46144.59652777778</v>
+        <v>46144.34652777778</v>
       </c>
       <c r="E191">
         <v>50476</v>
@@ -31421,7 +31421,7 @@
         <v>46144.34669229166</v>
       </c>
       <c r="D192" s="1">
-        <v>46144.59663194444</v>
+        <v>46144.34663194444</v>
       </c>
       <c r="E192">
         <v>50576</v>
@@ -31564,7 +31564,7 @@
         <v>46144.34689515046</v>
       </c>
       <c r="D193" s="1">
-        <v>46144.596875</v>
+        <v>46144.346875</v>
       </c>
       <c r="E193">
         <v>50994</v>
@@ -31707,7 +31707,7 @@
         <v>46144.34701017361</v>
       </c>
       <c r="D194" s="1">
-        <v>46144.596979166665</v>
+        <v>46144.346979166665</v>
       </c>
       <c r="E194">
         <v>51163</v>
@@ -31850,7 +31850,7 @@
         <v>46144.34724203704</v>
       </c>
       <c r="D195" s="1">
-        <v>46144.59722222222</v>
+        <v>46144.34722222222</v>
       </c>
       <c r="E195">
         <v>51658</v>
@@ -31993,7 +31993,7 @@
         <v>46144.347385775465</v>
       </c>
       <c r="D196" s="1">
-        <v>46144.59732638889</v>
+        <v>46144.34732638889</v>
       </c>
       <c r="E196">
         <v>51840</v>
@@ -32136,7 +32136,7 @@
         <v>46144.347469155095</v>
       </c>
       <c r="D197" s="1">
-        <v>46144.597453703704</v>
+        <v>46144.347453703704</v>
       </c>
       <c r="E197">
         <v>51975</v>
@@ -32258,7 +32258,7 @@
         <v>46144.34758958333</v>
       </c>
       <c r="D198" s="1">
-        <v>46144.59756944444</v>
+        <v>46144.34756944444</v>
       </c>
       <c r="E198">
         <v>52214</v>
@@ -32401,7 +32401,7 @@
         <v>46144.34770615741</v>
       </c>
       <c r="D199" s="1">
-        <v>46144.59767361111</v>
+        <v>46144.34767361111</v>
       </c>
       <c r="E199">
         <v>52375</v>
@@ -32544,7 +32544,7 @@
         <v>46144.3479375</v>
       </c>
       <c r="D200" s="1">
-        <v>46144.597916666666</v>
+        <v>46144.347916666666</v>
       </c>
       <c r="E200">
         <v>52960</v>
@@ -32687,7 +32687,7 @@
         <v>46144.34808082176</v>
       </c>
       <c r="D201" s="1">
-        <v>46144.598020833335</v>
+        <v>46144.348020833335</v>
       </c>
       <c r="E201">
         <v>53067</v>
@@ -32830,7 +32830,7 @@
         <v>46144.3482840625</v>
       </c>
       <c r="D202" s="1">
-        <v>46144.59826388889</v>
+        <v>46144.34826388889</v>
       </c>
       <c r="E202">
         <v>53418</v>
@@ -32973,7 +32973,7 @@
         <v>46144.34839869213</v>
       </c>
       <c r="D203" s="1">
-        <v>46144.59836805556</v>
+        <v>46144.34836805556</v>
       </c>
       <c r="E203">
         <v>53512</v>
@@ -33116,7 +33116,7 @@
         <v>46144.34863085648</v>
       </c>
       <c r="D204" s="1">
-        <v>46144.59861111111</v>
+        <v>46144.34861111111</v>
       </c>
       <c r="E204">
         <v>53852</v>
@@ -33259,7 +33259,7 @@
         <v>46144.34877</v>
       </c>
       <c r="D205" s="1">
-        <v>46144.598715277774</v>
+        <v>46144.348715277774</v>
       </c>
       <c r="E205">
         <v>53948</v>
@@ -33402,7 +33402,7 @@
         <v>46144.348978194444</v>
       </c>
       <c r="D206" s="1">
-        <v>46144.598958333336</v>
+        <v>46144.348958333336</v>
       </c>
       <c r="E206">
         <v>54265</v>
@@ -33545,7 +33545,7 @@
         <v>46144.349091724536</v>
       </c>
       <c r="D207" s="1">
-        <v>46144.5990625</v>
+        <v>46144.3490625</v>
       </c>
       <c r="E207">
         <v>54340</v>
@@ -33688,7 +33688,7 @@
         <v>46144.34932622685</v>
       </c>
       <c r="D208" s="1">
-        <v>46144.59930555556</v>
+        <v>46144.34930555556</v>
       </c>
       <c r="E208">
         <v>54702</v>
@@ -33831,7 +33831,7 @@
         <v>46144.34946765046</v>
       </c>
       <c r="D209" s="1">
-        <v>46144.59940972222</v>
+        <v>46144.34940972222</v>
       </c>
       <c r="E209">
         <v>54801</v>
@@ -33974,7 +33974,7 @@
         <v>46144.34967246528</v>
       </c>
       <c r="D210" s="1">
-        <v>46144.599652777775</v>
+        <v>46144.349652777775</v>
       </c>
       <c r="E210">
         <v>55135</v>
@@ -34117,7 +34117,7 @@
         <v>46144.349786875</v>
       </c>
       <c r="D211" s="1">
-        <v>46144.599756944444</v>
+        <v>46144.349756944444</v>
       </c>
       <c r="E211">
         <v>55228</v>
@@ -34260,7 +34260,7 @@
         <v>46144.350020590275</v>
       </c>
       <c r="D212" s="1">
-        <v>46144.6</v>
+        <v>46144.35</v>
       </c>
       <c r="E212">
         <v>55581</v>
@@ -34403,7 +34403,7 @@
         <v>46144.35016412037</v>
       </c>
       <c r="D213" s="1">
-        <v>46144.60010416667</v>
+        <v>46144.35010416667</v>
       </c>
       <c r="E213">
         <v>55681</v>
@@ -34546,7 +34546,7 @@
         <v>46144.350367025465</v>
       </c>
       <c r="D214" s="1">
-        <v>46144.60034722222</v>
+        <v>46144.35034722222</v>
       </c>
       <c r="E214">
         <v>56050</v>
@@ -34689,7 +34689,7 @@
         <v>46144.35048050926</v>
       </c>
       <c r="D215" s="1">
-        <v>46144.60045138889</v>
+        <v>46144.35045138889</v>
       </c>
       <c r="E215">
         <v>56129</v>
@@ -34832,7 +34832,7 @@
         <v>46144.35071452546</v>
       </c>
       <c r="D216" s="1">
-        <v>46144.600694444445</v>
+        <v>46144.350694444445</v>
       </c>
       <c r="E216">
         <v>56497</v>
@@ -34975,7 +34975,7 @@
         <v>46144.35085699074</v>
       </c>
       <c r="D217" s="1">
-        <v>46144.600798611114</v>
+        <v>46144.350798611114</v>
       </c>
       <c r="E217">
         <v>56622</v>
@@ -35118,7 +35118,7 @@
         <v>46144.35106228009</v>
       </c>
       <c r="D218" s="1">
-        <v>46144.60104166667</v>
+        <v>46144.35104166667</v>
       </c>
       <c r="E218">
         <v>57058</v>
@@ -35261,7 +35261,7 @@
         <v>46144.35117543981</v>
       </c>
       <c r="D219" s="1">
-        <v>46144.60114583333</v>
+        <v>46144.35114583333</v>
       </c>
       <c r="E219">
         <v>57175</v>
@@ -35404,7 +35404,7 @@
         <v>46144.351409537034</v>
       </c>
       <c r="D220" s="1">
-        <v>46144.60138888889</v>
+        <v>46144.35138888889</v>
       </c>
       <c r="E220">
         <v>57560</v>
@@ -35547,7 +35547,7 @@
         <v>46144.35155075231</v>
       </c>
       <c r="D221" s="1">
-        <v>46144.601493055554</v>
+        <v>46144.351493055554</v>
       </c>
       <c r="E221">
         <v>57656</v>
@@ -35690,7 +35690,7 @@
         <v>46144.35175664352</v>
       </c>
       <c r="D222" s="1">
-        <v>46144.60173611111</v>
+        <v>46144.35173611111</v>
       </c>
       <c r="E222">
         <v>58028</v>
@@ -35833,7 +35833,7 @@
         <v>46144.351869652775</v>
       </c>
       <c r="D223" s="1">
-        <v>46144.60184027778</v>
+        <v>46144.35184027778</v>
       </c>
       <c r="E223">
         <v>58143</v>
@@ -35976,7 +35976,7 @@
         <v>46144.35210452546</v>
       </c>
       <c r="D224" s="1">
-        <v>46144.60208333333</v>
+        <v>46144.35208333333</v>
       </c>
       <c r="E224">
         <v>58515</v>
@@ -36119,7 +36119,7 @@
         <v>46144.35224625</v>
       </c>
       <c r="D225" s="1">
-        <v>46144.6021875</v>
+        <v>46144.3521875</v>
       </c>
       <c r="E225">
         <v>58623</v>
@@ -36262,7 +36262,7 @@
         <v>46144.35233116898</v>
       </c>
       <c r="D226" s="1">
-        <v>46144.602314814816</v>
+        <v>46144.352314814816</v>
       </c>
       <c r="E226">
         <v>58757</v>
@@ -36384,7 +36384,7 @@
         <v>46144.35245082176</v>
       </c>
       <c r="D227" s="1">
-        <v>46144.602430555555</v>
+        <v>46144.352430555555</v>
       </c>
       <c r="E227">
         <v>58984</v>
@@ -36527,7 +36527,7 @@
         <v>46144.352564155095</v>
       </c>
       <c r="D228" s="1">
-        <v>46144.602534722224</v>
+        <v>46144.352534722224</v>
       </c>
       <c r="E228">
         <v>59116</v>
@@ -36670,7 +36670,7 @@
         <v>46144.352797719905</v>
       </c>
       <c r="D229" s="1">
-        <v>46144.60277777778</v>
+        <v>46144.35277777778</v>
       </c>
       <c r="E229">
         <v>59526</v>
@@ -36813,7 +36813,7 @@
         <v>46144.35294201389</v>
       </c>
       <c r="D230" s="1">
-        <v>46144.60288194445</v>
+        <v>46144.35288194445</v>
       </c>
       <c r="E230">
         <v>59623</v>
@@ -36956,7 +36956,7 @@
         <v>46144.35302486111</v>
       </c>
       <c r="D231" s="1">
-        <v>46144.60300925926</v>
+        <v>46144.35300925926</v>
       </c>
       <c r="E231">
         <v>59761</v>
@@ -37078,7 +37078,7 @@
         <v>46144.353145497684</v>
       </c>
       <c r="D232" s="1">
-        <v>46144.603125</v>
+        <v>46144.353125</v>
       </c>
       <c r="E232">
         <v>59999</v>
@@ -37221,7 +37221,7 @@
         <v>46144.35325974537</v>
       </c>
       <c r="D233" s="1">
-        <v>46144.60322916666</v>
+        <v>46144.35322916666</v>
       </c>
       <c r="E233">
         <v>60109</v>
@@ -37364,7 +37364,7 @@
         <v>46144.35337322917</v>
       </c>
       <c r="D234" s="1">
-        <v>46144.60335648148</v>
+        <v>46144.35335648148</v>
       </c>
       <c r="E234">
         <v>60237</v>
@@ -37486,7 +37486,7 @@
         <v>46144.35349269676</v>
       </c>
       <c r="D235" s="1">
-        <v>46144.603472222225</v>
+        <v>46144.353472222225</v>
       </c>
       <c r="E235">
         <v>60470</v>
@@ -37629,7 +37629,7 @@
         <v>46144.35363668981</v>
       </c>
       <c r="D236" s="1">
-        <v>46144.60357638889</v>
+        <v>46144.35357638889</v>
       </c>
       <c r="E236">
         <v>60572</v>
@@ -37772,7 +37772,7 @@
         <v>46144.35371826389</v>
       </c>
       <c r="D237" s="1">
-        <v>46144.6037037037</v>
+        <v>46144.3537037037</v>
       </c>
       <c r="E237">
         <v>60697</v>
@@ -37894,7 +37894,7 @@
         <v>46144.35384</v>
       </c>
       <c r="D238" s="1">
-        <v>46144.60381944444</v>
+        <v>46144.35381944444</v>
       </c>
       <c r="E238">
         <v>60949</v>
@@ -38037,7 +38037,7 @@
         <v>46144.35394896991</v>
       </c>
       <c r="D239" s="1">
-        <v>46144.60392361111</v>
+        <v>46144.35392361111</v>
       </c>
       <c r="E239">
         <v>61048</v>
@@ -38180,7 +38180,7 @@
         <v>46144.354186689816</v>
       </c>
       <c r="D240" s="1">
-        <v>46144.604166666664</v>
+        <v>46144.354166666664</v>
       </c>
       <c r="E240">
         <v>61433</v>
@@ -38323,7 +38323,7 @@
         <v>46144.35441172454</v>
       </c>
       <c r="D241" s="1">
-        <v>46144.60439814815</v>
+        <v>46144.35439814815</v>
       </c>
       <c r="E241">
         <v>61648</v>
@@ -38445,7 +38445,7 @@
         <v>46144.354534479164</v>
       </c>
       <c r="D242" s="1">
-        <v>46144.60451388889</v>
+        <v>46144.35451388889</v>
       </c>
       <c r="E242">
         <v>61904</v>
@@ -38588,7 +38588,7 @@
         <v>46144.35464363426</v>
       </c>
       <c r="D243" s="1">
-        <v>46144.60461805556</v>
+        <v>46144.35461805556</v>
       </c>
       <c r="E243">
         <v>62006</v>
@@ -38731,7 +38731,7 @@
         <v>46144.35488200231</v>
       </c>
       <c r="D244" s="1">
-        <v>46144.60486111111</v>
+        <v>46144.35486111111</v>
       </c>
       <c r="E244">
         <v>62402</v>
@@ -38874,7 +38874,7 @@
         <v>46144.35501987269</v>
       </c>
       <c r="D245" s="1">
-        <v>46144.60496527778</v>
+        <v>46144.35496527778</v>
       </c>
       <c r="E245">
         <v>62489</v>
@@ -39017,7 +39017,7 @@
         <v>46144.355106435185</v>
       </c>
       <c r="D246" s="1">
-        <v>46144.605092592596</v>
+        <v>46144.355092592596</v>
       </c>
       <c r="E246">
         <v>62616</v>
@@ -39139,7 +39139,7 @@
         <v>46144.35522804398</v>
       </c>
       <c r="D247" s="1">
-        <v>46144.605208333334</v>
+        <v>46144.355208333334</v>
       </c>
       <c r="E247">
         <v>62822</v>
@@ -39282,7 +39282,7 @@
         <v>46144.35533773148</v>
       </c>
       <c r="D248" s="1">
-        <v>46144.6053125</v>
+        <v>46144.3553125</v>
       </c>
       <c r="E248">
         <v>62954</v>
@@ -39425,7 +39425,7 @@
         <v>46144.355453460645</v>
       </c>
       <c r="D249" s="1">
-        <v>46144.60543981481</v>
+        <v>46144.35543981481</v>
       </c>
       <c r="E249">
         <v>63108</v>
@@ -39547,7 +39547,7 @@
         <v>46144.355576041664</v>
       </c>
       <c r="D250" s="1">
-        <v>46144.60555555556</v>
+        <v>46144.35555555556</v>
       </c>
       <c r="E250">
         <v>63339</v>
@@ -39690,7 +39690,7 @@
         <v>46144.35571351852</v>
       </c>
       <c r="D251" s="1">
-        <v>46144.60565972222</v>
+        <v>46144.35565972222</v>
       </c>
       <c r="E251">
         <v>63488</v>
@@ -39833,7 +39833,7 @@
         <v>46144.3558025463</v>
       </c>
       <c r="D252" s="1">
-        <v>46144.605787037035</v>
+        <v>46144.355787037035</v>
       </c>
       <c r="E252">
         <v>63653</v>
@@ -39955,7 +39955,7 @@
         <v>46144.35592263889</v>
       </c>
       <c r="D253" s="1">
-        <v>46144.60590277778</v>
+        <v>46144.35590277778</v>
       </c>
       <c r="E253">
         <v>63889</v>
@@ -40098,7 +40098,7 @@
         <v>46144.35603282407</v>
       </c>
       <c r="D254" s="1">
-        <v>46144.60600694444</v>
+        <v>46144.35600694444</v>
       </c>
       <c r="E254">
         <v>64001</v>
@@ -40241,7 +40241,7 @@
         <v>46144.35614795139</v>
       </c>
       <c r="D255" s="1">
-        <v>46144.60613425926</v>
+        <v>46144.35613425926</v>
       </c>
       <c r="E255">
         <v>64122</v>
@@ -40363,7 +40363,7 @@
         <v>46144.35627222222</v>
       </c>
       <c r="D256" s="1">
-        <v>46144.60625</v>
+        <v>46144.35625</v>
       </c>
       <c r="E256">
         <v>64363</v>
@@ -40506,7 +40506,7 @@
         <v>46144.356408368054</v>
       </c>
       <c r="D257" s="1">
-        <v>46144.606354166666</v>
+        <v>46144.356354166666</v>
       </c>
       <c r="E257">
         <v>64463</v>
@@ -40649,7 +40649,7 @@
         <v>46144.35649525463</v>
       </c>
       <c r="D258" s="1">
-        <v>46144.60648148148</v>
+        <v>46144.35648148148</v>
       </c>
       <c r="E258">
         <v>64601</v>
@@ -40771,7 +40771,7 @@
         <v>46144.35661768518</v>
       </c>
       <c r="D259" s="1">
-        <v>46144.60659722222</v>
+        <v>46144.35659722222</v>
       </c>
       <c r="E259">
         <v>64836</v>
@@ -40914,7 +40914,7 @@
         <v>46144.356728136576</v>
       </c>
       <c r="D260" s="1">
-        <v>46144.60670138889</v>
+        <v>46144.35670138889</v>
       </c>
       <c r="E260">
         <v>64938</v>
@@ -41057,7 +41057,7 @@
         <v>46144.35684234954</v>
       </c>
       <c r="D261" s="1">
-        <v>46144.606828703705</v>
+        <v>46144.356828703705</v>
       </c>
       <c r="E261">
         <v>65120</v>
@@ -41179,7 +41179,7 @@
         <v>46144.356964722225</v>
       </c>
       <c r="D262" s="1">
-        <v>46144.606944444444</v>
+        <v>46144.356944444444</v>
       </c>
       <c r="E262">
         <v>65375</v>
@@ -41322,7 +41322,7 @@
         <v>46144.357104016206</v>
       </c>
       <c r="D263" s="1">
-        <v>46144.60704861111</v>
+        <v>46144.35704861111</v>
       </c>
       <c r="E263">
         <v>65496</v>
@@ -41465,7 +41465,7 @@
         <v>46144.35731247685</v>
       </c>
       <c r="D264" s="1">
-        <v>46144.60729166667</v>
+        <v>46144.35729166667</v>
       </c>
       <c r="E264">
         <v>65855</v>
@@ -41608,7 +41608,7 @@
         <v>46144.357423009256</v>
       </c>
       <c r="D265" s="1">
-        <v>46144.607395833336</v>
+        <v>46144.357395833336</v>
       </c>
       <c r="E265">
         <v>65993</v>
@@ -41751,7 +41751,7 @@
         <v>46144.35753850694</v>
       </c>
       <c r="D266" s="1">
-        <v>46144.607523148145</v>
+        <v>46144.357523148145</v>
       </c>
       <c r="E266">
         <v>66140</v>
@@ -41873,7 +41873,7 @@
         <v>46144.357659166664</v>
       </c>
       <c r="D267" s="1">
-        <v>46144.60763888889</v>
+        <v>46144.35763888889</v>
       </c>
       <c r="E267">
         <v>66389</v>
@@ -42016,7 +42016,7 @@
         <v>46144.35780009259</v>
       </c>
       <c r="D268" s="1">
-        <v>46144.60774305555</v>
+        <v>46144.35774305555</v>
       </c>
       <c r="E268">
         <v>66506</v>
@@ -42159,7 +42159,7 @@
         <v>46144.358006608796</v>
       </c>
       <c r="D269" s="1">
-        <v>46144.607986111114</v>
+        <v>46144.357986111114</v>
       </c>
       <c r="E269">
         <v>66902</v>
@@ -42302,7 +42302,7 @@
         <v>46144.358116793985</v>
       </c>
       <c r="D270" s="1">
-        <v>46144.608090277776</v>
+        <v>46144.358090277776</v>
       </c>
       <c r="E270">
         <v>67025</v>
@@ -42445,7 +42445,7 @@
         <v>46144.358233784726</v>
       </c>
       <c r="D271" s="1">
-        <v>46144.60821759259</v>
+        <v>46144.35821759259</v>
       </c>
       <c r="E271">
         <v>67170</v>
@@ -42567,7 +42567,7 @@
         <v>46144.358354027776</v>
       </c>
       <c r="D272" s="1">
-        <v>46144.60833333333</v>
+        <v>46144.35833333333</v>
       </c>
       <c r="E272">
         <v>67424</v>
@@ -42710,7 +42710,7 @@
         <v>46144.358700439814</v>
       </c>
       <c r="D273" s="1">
-        <v>46144.60868055555</v>
+        <v>46144.35868055555</v>
       </c>
       <c r="E273">
         <v>67963</v>
@@ -42853,7 +42853,7 @@
         <v>46144.35881199074</v>
       </c>
       <c r="D274" s="1">
-        <v>46144.60878472222</v>
+        <v>46144.35878472222</v>
       </c>
       <c r="E274">
         <v>68076</v>
@@ -42996,7 +42996,7 @@
         <v>46144.35892711805</v>
       </c>
       <c r="D275" s="1">
-        <v>46144.60891203704</v>
+        <v>46144.35891203704</v>
       </c>
       <c r="E275">
         <v>68253</v>
@@ -43118,7 +43118,7 @@
         <v>46144.35904837963</v>
       </c>
       <c r="D276" s="1">
-        <v>46144.60902777778</v>
+        <v>46144.35902777778</v>
       </c>
       <c r="E276">
         <v>68505</v>
@@ -43261,7 +43261,7 @@
         <v>46144.359188912036</v>
       </c>
       <c r="D277" s="1">
-        <v>46144.609131944446</v>
+        <v>46144.359131944446</v>
       </c>
       <c r="E277">
         <v>68622</v>
@@ -43404,7 +43404,7 @@
         <v>46144.35927475694</v>
       </c>
       <c r="D278" s="1">
-        <v>46144.60925925926</v>
+        <v>46144.35925925926</v>
       </c>
       <c r="E278">
         <v>68788</v>
@@ -43526,7 +43526,7 @@
         <v>46144.359395</v>
       </c>
       <c r="D279" s="1">
-        <v>46144.609375</v>
+        <v>46144.359375</v>
       </c>
       <c r="E279">
         <v>69042</v>
@@ -43669,7 +43669,7 @@
         <v>46144.3595069213</v>
       </c>
       <c r="D280" s="1">
-        <v>46144.60947916667</v>
+        <v>46144.35947916667</v>
       </c>
       <c r="E280">
         <v>69169</v>
@@ -43812,7 +43812,7 @@
         <v>46144.359742546294</v>
       </c>
       <c r="D281" s="1">
-        <v>46144.60972222222</v>
+        <v>46144.35972222222</v>
       </c>
       <c r="E281">
         <v>69577</v>
@@ -43955,7 +43955,7 @@
         <v>46144.35988310185</v>
       </c>
       <c r="D282" s="1">
-        <v>46144.609826388885</v>
+        <v>46144.359826388885</v>
       </c>
       <c r="E282">
         <v>69723</v>
@@ -44098,7 +44098,7 @@
         <v>46144.36009096065</v>
       </c>
       <c r="D283" s="1">
-        <v>46144.61006944445</v>
+        <v>46144.36006944445</v>
       </c>
       <c r="E283">
         <v>70109</v>
@@ -44241,7 +44241,7 @@
         <v>46144.36020038195</v>
       </c>
       <c r="D284" s="1">
-        <v>46144.61017361111</v>
+        <v>46144.36017361111</v>
       </c>
       <c r="E284">
         <v>70240</v>
@@ -44384,7 +44384,7 @@
         <v>46144.36043741898</v>
       </c>
       <c r="D285" s="1">
-        <v>46144.61041666667</v>
+        <v>46144.36041666667</v>
       </c>
       <c r="E285">
         <v>70640</v>
@@ -44527,7 +44527,7 @@
         <v>46144.36057697917</v>
       </c>
       <c r="D286" s="1">
-        <v>46144.61052083333</v>
+        <v>46144.36052083333</v>
       </c>
       <c r="E286">
         <v>70757</v>
@@ -44670,7 +44670,7 @@
         <v>46144.36066332176</v>
       </c>
       <c r="D287" s="1">
-        <v>46144.61064814815</v>
+        <v>46144.36064814815</v>
       </c>
       <c r="E287">
         <v>70872</v>
@@ -44792,7 +44792,7 @@
         <v>46144.36078420139</v>
       </c>
       <c r="D288" s="1">
-        <v>46144.610763888886</v>
+        <v>46144.360763888886</v>
       </c>
       <c r="E288">
         <v>71138</v>
@@ -44935,7 +44935,7 @@
         <v>46144.36101021991</v>
       </c>
       <c r="D289" s="1">
-        <v>46144.61099537037</v>
+        <v>46144.36099537037</v>
       </c>
       <c r="E289">
         <v>71413</v>
@@ -45057,7 +45057,7 @@
         <v>46144.361131666665</v>
       </c>
       <c r="D290" s="1">
-        <v>46144.61111111111</v>
+        <v>46144.36111111111</v>
       </c>
       <c r="E290">
         <v>71655</v>
@@ -45200,7 +45200,7 @@
         <v>46144.36127378472</v>
       </c>
       <c r="D291" s="1">
-        <v>46144.61121527778</v>
+        <v>46144.36121527778</v>
       </c>
       <c r="E291">
         <v>71784</v>
@@ -45343,7 +45343,7 @@
         <v>46144.36147833333</v>
       </c>
       <c r="D292" s="1">
-        <v>46144.61145833333</v>
+        <v>46144.36145833333</v>
       </c>
       <c r="E292">
         <v>72210</v>
@@ -45486,7 +45486,7 @@
         <v>46144.36159195602</v>
       </c>
       <c r="D293" s="1">
-        <v>46144.6115625</v>
+        <v>46144.3615625</v>
       </c>
       <c r="E293">
         <v>72302</v>
@@ -45629,7 +45629,7 @@
         <v>46144.3617053125</v>
       </c>
       <c r="D294" s="1">
-        <v>46144.61168981482</v>
+        <v>46144.36168981482</v>
       </c>
       <c r="E294">
         <v>72480</v>
@@ -45751,7 +45751,7 @@
         <v>46144.36182666667</v>
       </c>
       <c r="D295" s="1">
-        <v>46144.611805555556</v>
+        <v>46144.361805555556</v>
       </c>
       <c r="E295">
         <v>72711</v>
@@ -45894,7 +45894,7 @@
         <v>46144.36196890046</v>
       </c>
       <c r="D296" s="1">
-        <v>46144.611909722225</v>
+        <v>46144.361909722225</v>
       </c>
       <c r="E296">
         <v>72842</v>
@@ -46037,7 +46037,7 @@
         <v>46144.362052627315</v>
       </c>
       <c r="D297" s="1">
-        <v>46144.61203703703</v>
+        <v>46144.36203703703</v>
       </c>
       <c r="E297">
         <v>73001</v>
@@ -46159,7 +46159,7 @@
         <v>46144.362173472226</v>
       </c>
       <c r="D298" s="1">
-        <v>46144.61215277778</v>
+        <v>46144.36215277778</v>
       </c>
       <c r="E298">
         <v>73255</v>
@@ -46302,7 +46302,7 @@
         <v>46144.36228693287</v>
       </c>
       <c r="D299" s="1">
-        <v>46144.61225694444</v>
+        <v>46144.36225694444</v>
       </c>
       <c r="E299">
         <v>73410</v>
@@ -46445,7 +46445,7 @@
         <v>46144.36251980324</v>
       </c>
       <c r="D300" s="1">
-        <v>46144.6125</v>
+        <v>46144.3625</v>
       </c>
       <c r="E300">
         <v>73871</v>
@@ -46588,7 +46588,7 @@
         <v>46144.362663113425</v>
       </c>
       <c r="D301" s="1">
-        <v>46144.612604166665</v>
+        <v>46144.362604166665</v>
       </c>
       <c r="E301">
         <v>74004</v>
@@ -46731,7 +46731,7 @@
         <v>46144.36286784722</v>
       </c>
       <c r="D302" s="1">
-        <v>46144.61284722222</v>
+        <v>46144.36284722222</v>
       </c>
       <c r="E302">
         <v>74406</v>
@@ -46874,7 +46874,7 @@
         <v>46144.36298074074</v>
       </c>
       <c r="D303" s="1">
-        <v>46144.61295138889</v>
+        <v>46144.36295138889</v>
       </c>
       <c r="E303">
         <v>74554</v>
@@ -47017,7 +47017,7 @@
         <v>46144.363214861114</v>
       </c>
       <c r="D304" s="1">
-        <v>46144.61319444444</v>
+        <v>46144.36319444444</v>
       </c>
       <c r="E304">
         <v>74979</v>
@@ -47160,7 +47160,7 @@
         <v>46144.363357662034</v>
       </c>
       <c r="D305" s="1">
-        <v>46144.61329861111</v>
+        <v>46144.36329861111</v>
       </c>
       <c r="E305">
         <v>75103</v>
@@ -47303,7 +47303,7 @@
         <v>46144.36344116898</v>
       </c>
       <c r="D306" s="1">
-        <v>46144.61342592593</v>
+        <v>46144.36342592593</v>
       </c>
       <c r="E306">
         <v>75282</v>
@@ -47425,7 +47425,7 @@
         <v>46144.363561909726</v>
       </c>
       <c r="D307" s="1">
-        <v>46144.613541666666</v>
+        <v>46144.363541666666</v>
       </c>
       <c r="E307">
         <v>75528</v>
@@ -47568,7 +47568,7 @@
         <v>46144.363675243054</v>
       </c>
       <c r="D308" s="1">
-        <v>46144.613645833335</v>
+        <v>46144.363645833335</v>
       </c>
       <c r="E308">
         <v>75622</v>
@@ -47711,7 +47711,7 @@
         <v>46144.36378796296</v>
       </c>
       <c r="D309" s="1">
-        <v>46144.61377314815</v>
+        <v>46144.36377314815</v>
       </c>
       <c r="E309">
         <v>75803</v>
@@ -47833,7 +47833,7 @@
         <v>46144.36390962963</v>
       </c>
       <c r="D310" s="1">
-        <v>46144.61388888889</v>
+        <v>46144.36388888889</v>
       </c>
       <c r="E310">
         <v>76050</v>
@@ -47976,7 +47976,7 @@
         <v>46144.36405174769</v>
       </c>
       <c r="D311" s="1">
-        <v>46144.61399305556</v>
+        <v>46144.36399305556</v>
       </c>
       <c r="E311">
         <v>76187</v>
@@ -48119,7 +48119,7 @@
         <v>46144.36413501157</v>
       </c>
       <c r="D312" s="1">
-        <v>46144.614120370374</v>
+        <v>46144.364120370374</v>
       </c>
       <c r="E312">
         <v>76355</v>
@@ -48241,7 +48241,7 @@
         <v>46144.364255162036</v>
       </c>
       <c r="D313" s="1">
-        <v>46144.61423611111</v>
+        <v>46144.36423611111</v>
       </c>
       <c r="E313">
         <v>76616</v>
@@ -48384,7 +48384,7 @@
         <v>46144.36437079861</v>
       </c>
       <c r="D314" s="1">
-        <v>46144.614340277774</v>
+        <v>46144.364340277774</v>
       </c>
       <c r="E314">
         <v>76721</v>
@@ -48527,7 +48527,7 @@
         <v>46144.36448379629</v>
       </c>
       <c r="D315" s="1">
-        <v>46144.61446759259</v>
+        <v>46144.36446759259</v>
       </c>
       <c r="E315">
         <v>76903</v>
@@ -48649,7 +48649,7 @@
         <v>46144.36460366898</v>
       </c>
       <c r="D316" s="1">
-        <v>46144.614583333336</v>
+        <v>46144.364583333336</v>
       </c>
       <c r="E316">
         <v>77164</v>
@@ -48792,7 +48792,7 @@
         <v>46144.36474600695</v>
       </c>
       <c r="D317" s="1">
-        <v>46144.6146875</v>
+        <v>46144.3646875</v>
       </c>
       <c r="E317">
         <v>77285</v>
@@ -48935,7 +48935,7 @@
         <v>46144.36483226852</v>
       </c>
       <c r="D318" s="1">
-        <v>46144.61481481481</v>
+        <v>46144.36481481481</v>
       </c>
       <c r="E318">
         <v>77451</v>
@@ -49057,7 +49057,7 @@
         <v>46144.3649509375</v>
       </c>
       <c r="D319" s="1">
-        <v>46144.61493055556</v>
+        <v>46144.36493055556</v>
       </c>
       <c r="E319">
         <v>77712</v>
@@ -49200,7 +49200,7 @@
         <v>46144.3650646875</v>
       </c>
       <c r="D320" s="1">
-        <v>46144.61503472222</v>
+        <v>46144.36503472222</v>
       </c>
       <c r="E320">
         <v>77844</v>
@@ -49343,7 +49343,7 @@
         <v>46144.36517828704</v>
       </c>
       <c r="D321" s="1">
-        <v>46144.61516203704</v>
+        <v>46144.36516203704</v>
       </c>
       <c r="E321">
         <v>78025</v>
@@ -49465,7 +49465,7 @@
         <v>46144.36529829861</v>
       </c>
       <c r="D322" s="1">
-        <v>46144.615277777775</v>
+        <v>46144.365277777775</v>
       </c>
       <c r="E322">
         <v>78299</v>
@@ -49608,7 +49608,7 @@
         <v>46144.36544072917</v>
       </c>
       <c r="D323" s="1">
-        <v>46144.615381944444</v>
+        <v>46144.365381944444</v>
       </c>
       <c r="E323">
         <v>78462</v>
@@ -49751,7 +49751,7 @@
         <v>46144.36552385417</v>
       </c>
       <c r="D324" s="1">
-        <v>46144.61550925926</v>
+        <v>46144.36550925926</v>
       </c>
       <c r="E324">
         <v>78629</v>
@@ -49873,7 +49873,7 @@
         <v>46144.36564497685</v>
       </c>
       <c r="D325" s="1">
-        <v>46144.615625</v>
+        <v>46144.365625</v>
       </c>
       <c r="E325">
         <v>78900</v>
@@ -50016,7 +50016,7 @@
         <v>46144.365758900465</v>
       </c>
       <c r="D326" s="1">
-        <v>46144.61572916667</v>
+        <v>46144.36572916667</v>
       </c>
       <c r="E326">
         <v>79042</v>
@@ -50159,7 +50159,7 @@
         <v>46144.36587295139</v>
       </c>
       <c r="D327" s="1">
-        <v>46144.61585648148</v>
+        <v>46144.36585648148</v>
       </c>
       <c r="E327">
         <v>79226</v>
@@ -50281,7 +50281,7 @@
         <v>46144.36599225694</v>
       </c>
       <c r="D328" s="1">
-        <v>46144.61597222222</v>
+        <v>46144.36597222222</v>
       </c>
       <c r="E328">
         <v>79470</v>
@@ -50424,7 +50424,7 @@
         <v>46144.3661346875</v>
       </c>
       <c r="D329" s="1">
-        <v>46144.61607638889</v>
+        <v>46144.36607638889</v>
       </c>
       <c r="E329">
         <v>79601</v>
@@ -50567,7 +50567,7 @@
         <v>46144.36622211806</v>
       </c>
       <c r="D330" s="1">
-        <v>46144.61620370371</v>
+        <v>46144.36620370371</v>
       </c>
       <c r="E330">
         <v>79744</v>
@@ -50689,7 +50689,7 @@
         <v>46144.36633951389</v>
       </c>
       <c r="D331" s="1">
-        <v>46144.616319444445</v>
+        <v>46144.366319444445</v>
       </c>
       <c r="E331">
         <v>80007</v>
@@ -50832,7 +50832,7 @@
         <v>46144.36645274305</v>
       </c>
       <c r="D332" s="1">
-        <v>46144.616423611114</v>
+        <v>46144.366423611114</v>
       </c>
       <c r="E332">
         <v>80154</v>
@@ -50975,7 +50975,7 @@
         <v>46144.36668702546</v>
       </c>
       <c r="D333" s="1">
-        <v>46144.61666666667</v>
+        <v>46144.36666666667</v>
       </c>
       <c r="E333">
         <v>80578</v>
@@ -51118,7 +51118,7 @@
         <v>46144.366830162035</v>
       </c>
       <c r="D334" s="1">
-        <v>46144.61677083333</v>
+        <v>46144.36677083333</v>
       </c>
       <c r="E334">
         <v>80720</v>
@@ -51261,7 +51261,7 @@
         <v>46144.366913784725</v>
       </c>
       <c r="D335" s="1">
-        <v>46144.616898148146</v>
+        <v>46144.366898148146</v>
       </c>
       <c r="E335">
         <v>80876</v>
@@ -51383,7 +51383,7 @@
         <v>46144.36703412037</v>
       </c>
       <c r="D336" s="1">
-        <v>46144.61701388889</v>
+        <v>46144.36701388889</v>
       </c>
       <c r="E336">
         <v>81161</v>
@@ -51526,7 +51526,7 @@
         <v>46144.36714814815</v>
       </c>
       <c r="D337" s="1">
-        <v>46144.617118055554</v>
+        <v>46144.367118055554</v>
       </c>
       <c r="E337">
         <v>81313</v>
@@ -51669,7 +51669,7 @@
         <v>46144.367381840275</v>
       </c>
       <c r="D338" s="1">
-        <v>46144.61736111111</v>
+        <v>46144.36736111111</v>
       </c>
       <c r="E338">
         <v>81838</v>
@@ -51812,7 +51812,7 @@
         <v>46144.367524849535</v>
       </c>
       <c r="D339" s="1">
-        <v>46144.61746527778</v>
+        <v>46144.36746527778</v>
       </c>
       <c r="E339">
         <v>81987</v>
@@ -51955,7 +51955,7 @@
         <v>46144.36761048611</v>
       </c>
       <c r="D340" s="1">
-        <v>46144.61759259259</v>
+        <v>46144.36759259259</v>
       </c>
       <c r="E340">
         <v>82136</v>
@@ -52077,7 +52077,7 @@
         <v>46144.36772925926</v>
       </c>
       <c r="D341" s="1">
-        <v>46144.61770833333</v>
+        <v>46144.36770833333</v>
       </c>
       <c r="E341">
         <v>82426</v>
@@ -52220,7 +52220,7 @@
         <v>46144.36784275463</v>
       </c>
       <c r="D342" s="1">
-        <v>46144.6178125</v>
+        <v>46144.3678125</v>
       </c>
       <c r="E342">
         <v>82591</v>
@@ -52363,7 +52363,7 @@
         <v>46144.368075162034</v>
       </c>
       <c r="D343" s="1">
-        <v>46144.618055555555</v>
+        <v>46144.368055555555</v>
       </c>
       <c r="E343">
         <v>83028</v>
@@ -52506,7 +52506,7 @@
         <v>46144.36821881944</v>
       </c>
       <c r="D344" s="1">
-        <v>46144.618159722224</v>
+        <v>46144.368159722224</v>
       </c>
       <c r="E344">
         <v>83165</v>
@@ -52649,7 +52649,7 @@
         <v>46144.36842298611</v>
       </c>
       <c r="D345" s="1">
-        <v>46144.61840277778</v>
+        <v>46144.36840277778</v>
       </c>
       <c r="E345">
         <v>83594</v>
@@ -52792,7 +52792,7 @@
         <v>46144.36853929398</v>
       </c>
       <c r="D346" s="1">
-        <v>46144.61850694445</v>
+        <v>46144.36850694445</v>
       </c>
       <c r="E346">
         <v>83734</v>
@@ -52935,7 +52935,7 @@
         <v>46144.36876979167</v>
       </c>
       <c r="D347" s="1">
-        <v>46144.61875</v>
+        <v>46144.36875</v>
       </c>
       <c r="E347">
         <v>84135</v>
@@ -53078,7 +53078,7 @@
         <v>46144.3689121875</v>
       </c>
       <c r="D348" s="1">
-        <v>46144.61885416666</v>
+        <v>46144.36885416666</v>
       </c>
       <c r="E348">
         <v>84275</v>
@@ -53221,7 +53221,7 @@
         <v>46144.36911688658</v>
       </c>
       <c r="D349" s="1">
-        <v>46144.619097222225</v>
+        <v>46144.369097222225</v>
       </c>
       <c r="E349">
         <v>84686</v>
@@ -53364,7 +53364,7 @@
         <v>46144.36923076389</v>
       </c>
       <c r="D350" s="1">
-        <v>46144.61920138889</v>
+        <v>46144.36920138889</v>
       </c>
       <c r="E350">
         <v>84837</v>
@@ -53507,7 +53507,7 @@
         <v>46144.36934680556</v>
       </c>
       <c r="D351" s="1">
-        <v>46144.6193287037</v>
+        <v>46144.3693287037</v>
       </c>
       <c r="E351">
         <v>84994</v>
@@ -53629,7 +53629,7 @@
         <v>46144.36946415509</v>
       </c>
       <c r="D352" s="1">
-        <v>46144.61944444444</v>
+        <v>46144.36944444444</v>
       </c>
       <c r="E352">
         <v>85252</v>
@@ -53772,7 +53772,7 @@
         <v>46144.3696071875</v>
       </c>
       <c r="D353" s="1">
-        <v>46144.61954861111</v>
+        <v>46144.36954861111</v>
       </c>
       <c r="E353">
         <v>85392</v>
@@ -53915,7 +53915,7 @@
         <v>46144.36981074074</v>
       </c>
       <c r="D354" s="1">
-        <v>46144.619791666664</v>
+        <v>46144.369791666664</v>
       </c>
       <c r="E354">
         <v>85835</v>
@@ -54058,7 +54058,7 @@
         <v>46144.370039525464</v>
       </c>
       <c r="D355" s="1">
-        <v>46144.62002314815</v>
+        <v>46144.37002314815</v>
       </c>
       <c r="E355">
         <v>86123</v>
@@ -54180,7 +54180,7 @@
         <v>46144.37015872685</v>
       </c>
       <c r="D356" s="1">
-        <v>46144.62013888889</v>
+        <v>46144.37013888889</v>
       </c>
       <c r="E356">
         <v>86390</v>
@@ -54323,7 +54323,7 @@
         <v>46144.37030142361</v>
       </c>
       <c r="D357" s="1">
-        <v>46144.62024305556</v>
+        <v>46144.37024305556</v>
       </c>
       <c r="E357">
         <v>86511</v>
@@ -54466,7 +54466,7 @@
         <v>46144.370506238425</v>
       </c>
       <c r="D358" s="1">
-        <v>46144.62048611111</v>
+        <v>46144.37048611111</v>
       </c>
       <c r="E358">
         <v>86929</v>
@@ -54609,7 +54609,7 @@
         <v>46144.37061988426</v>
       </c>
       <c r="D359" s="1">
-        <v>46144.62059027778</v>
+        <v>46144.37059027778</v>
       </c>
       <c r="E359">
         <v>87056</v>
@@ -54752,7 +54752,7 @@
         <v>46144.370733090276</v>
       </c>
       <c r="D360" s="1">
-        <v>46144.620717592596</v>
+        <v>46144.370717592596</v>
       </c>
       <c r="E360">
         <v>87219</v>
@@ -54874,7 +54874,7 @@
         <v>46144.37085291667</v>
       </c>
       <c r="D361" s="1">
-        <v>46144.620833333334</v>
+        <v>46144.370833333334</v>
       </c>
       <c r="E361">
         <v>87487</v>
@@ -55017,7 +55017,7 @@
         <v>46144.37099619213</v>
       </c>
       <c r="D362" s="1">
-        <v>46144.6209375</v>
+        <v>46144.3709375</v>
       </c>
       <c r="E362">
         <v>87649</v>
@@ -55160,7 +55160,7 @@
         <v>46144.37107998843</v>
       </c>
       <c r="D363" s="1">
-        <v>46144.62106481481</v>
+        <v>46144.37106481481</v>
       </c>
       <c r="E363">
         <v>87816</v>
@@ -55282,7 +55282,7 @@
         <v>46144.37120003472</v>
       </c>
       <c r="D364" s="1">
-        <v>46144.62118055556</v>
+        <v>46144.37118055556</v>
       </c>
       <c r="E364">
         <v>88087</v>
@@ -55425,7 +55425,7 @@
         <v>46144.37131458333</v>
       </c>
       <c r="D365" s="1">
-        <v>46144.62128472222</v>
+        <v>46144.37128472222</v>
       </c>
       <c r="E365">
         <v>88238</v>
@@ -55568,7 +55568,7 @@
         <v>46144.371429722225</v>
       </c>
       <c r="D366" s="1">
-        <v>46144.621412037035</v>
+        <v>46144.371412037035</v>
       </c>
       <c r="E366">
         <v>88410</v>
@@ -55690,7 +55690,7 @@
         <v>46144.37154789352</v>
       </c>
       <c r="D367" s="1">
-        <v>46144.62152777778</v>
+        <v>46144.37152777778</v>
       </c>
       <c r="E367">
         <v>88678</v>
@@ -55833,7 +55833,7 @@
         <v>46144.37169020833</v>
       </c>
       <c r="D368" s="1">
-        <v>46144.62163194444</v>
+        <v>46144.37163194444</v>
       </c>
       <c r="E368">
         <v>88830</v>
@@ -55976,7 +55976,7 @@
         <v>46144.37189511574</v>
       </c>
       <c r="D369" s="1">
-        <v>46144.621875</v>
+        <v>46144.371875</v>
       </c>
       <c r="E369">
         <v>89263</v>
@@ -56119,7 +56119,7 @@
         <v>46144.372008900464</v>
       </c>
       <c r="D370" s="1">
-        <v>46144.621979166666</v>
+        <v>46144.371979166666</v>
       </c>
       <c r="E370">
         <v>89395</v>
@@ -56262,7 +56262,7 @@
         <v>46144.37212208333</v>
       </c>
       <c r="D371" s="1">
-        <v>46144.62210648148</v>
+        <v>46144.37210648148</v>
       </c>
       <c r="E371">
         <v>89558</v>
@@ -56384,7 +56384,7 @@
         <v>46144.37224179398</v>
       </c>
       <c r="D372" s="1">
-        <v>46144.62222222222</v>
+        <v>46144.37222222222</v>
       </c>
       <c r="E372">
         <v>89810</v>
@@ -56527,7 +56527,7 @@
         <v>46144.37238472222</v>
       </c>
       <c r="D373" s="1">
-        <v>46144.62232638889</v>
+        <v>46144.37232638889</v>
       </c>
       <c r="E373">
         <v>89948</v>
@@ -56670,7 +56670,7 @@
         <v>46144.372470393515</v>
       </c>
       <c r="D374" s="1">
-        <v>46144.622453703705</v>
+        <v>46144.372453703705</v>
       </c>
       <c r="E374">
         <v>90103</v>
@@ -56792,7 +56792,7 @@
         <v>46144.37258924769</v>
       </c>
       <c r="D375" s="1">
-        <v>46144.622569444444</v>
+        <v>46144.372569444444</v>
       </c>
       <c r="E375">
         <v>90387</v>
@@ -56935,7 +56935,7 @@
         <v>46144.37270354167</v>
       </c>
       <c r="D376" s="1">
-        <v>46144.62267361111</v>
+        <v>46144.37267361111</v>
       </c>
       <c r="E376">
         <v>90520</v>
@@ -57078,7 +57078,7 @@
         <v>46144.372817662035</v>
       </c>
       <c r="D377" s="1">
-        <v>46144.62280092593</v>
+        <v>46144.37280092593</v>
       </c>
       <c r="E377">
         <v>90681</v>
@@ -57200,7 +57200,7 @@
         <v>46144.37293607639</v>
       </c>
       <c r="D378" s="1">
-        <v>46144.62291666667</v>
+        <v>46144.37291666667</v>
       </c>
       <c r="E378">
         <v>90936</v>
@@ -57343,7 +57343,7 @@
         <v>46144.373079895835</v>
       </c>
       <c r="D379" s="1">
-        <v>46144.623020833336</v>
+        <v>46144.373020833336</v>
       </c>
       <c r="E379">
         <v>91072</v>
@@ -57486,7 +57486,7 @@
         <v>46144.37316387732</v>
       </c>
       <c r="D380" s="1">
-        <v>46144.623148148145</v>
+        <v>46144.373148148145</v>
       </c>
       <c r="E380">
         <v>91225</v>
@@ -57608,7 +57608,7 @@
         <v>46144.3732846412</v>
       </c>
       <c r="D381" s="1">
-        <v>46144.62326388889</v>
+        <v>46144.37326388889</v>
       </c>
       <c r="E381">
         <v>91496</v>
@@ -57751,7 +57751,7 @@
         <v>46144.373397766205</v>
       </c>
       <c r="D382" s="1">
-        <v>46144.62336805555</v>
+        <v>46144.37336805555</v>
       </c>
       <c r="E382">
         <v>91623</v>
@@ -57894,7 +57894,7 @@
         <v>46144.373511770835</v>
       </c>
       <c r="D383" s="1">
-        <v>46144.62349537037</v>
+        <v>46144.37349537037</v>
       </c>
       <c r="E383">
         <v>91754</v>
@@ -58016,7 +58016,7 @@
         <v>46144.37363322917</v>
       </c>
       <c r="D384" s="1">
-        <v>46144.623611111114</v>
+        <v>46144.373611111114</v>
       </c>
       <c r="E384">
         <v>92001</v>
@@ -58159,7 +58159,7 @@
         <v>46144.373774050924</v>
       </c>
       <c r="D385" s="1">
-        <v>46144.623715277776</v>
+        <v>46144.373715277776</v>
       </c>
       <c r="E385">
         <v>92116</v>
@@ -58302,7 +58302,7 @@
         <v>46144.373978564814</v>
       </c>
       <c r="D386" s="1">
-        <v>46144.62395833333</v>
+        <v>46144.37395833333</v>
       </c>
       <c r="E386">
         <v>92520</v>
@@ -58445,7 +58445,7 @@
         <v>46144.374092094906</v>
       </c>
       <c r="D387" s="1">
-        <v>46144.6240625</v>
+        <v>46144.3740625</v>
       </c>
       <c r="E387">
         <v>92649</v>
@@ -58588,7 +58588,7 @@
         <v>46144.3743256713</v>
       </c>
       <c r="D388" s="1">
-        <v>46144.62430555555</v>
+        <v>46144.37430555555</v>
       </c>
       <c r="E388">
         <v>93054</v>
@@ -58731,7 +58731,7 @@
         <v>46144.37447181713</v>
       </c>
       <c r="D389" s="1">
-        <v>46144.62440972222</v>
+        <v>46144.37440972222</v>
       </c>
       <c r="E389">
         <v>93187</v>
@@ -58874,7 +58874,7 @@
         <v>46144.37456420139</v>
       </c>
       <c r="D390" s="1">
-        <v>46144.624548611115</v>
+        <v>46144.374548611115</v>
       </c>
       <c r="E390">
         <v>93352</v>
@@ -58996,7 +58996,7 @@
         <v>46144.374673715276</v>
       </c>
       <c r="D391" s="1">
-        <v>46144.62465277778</v>
+        <v>46144.37465277778</v>
       </c>
       <c r="E391">
         <v>93575</v>
@@ -59139,7 +59139,7 @@
         <v>46144.37478775463</v>
       </c>
       <c r="D392" s="1">
-        <v>46144.624756944446</v>
+        <v>46144.374756944446</v>
       </c>
       <c r="E392">
         <v>93697</v>
@@ -59282,7 +59282,7 @@
         <v>46144.375020011576</v>
       </c>
       <c r="D393" s="1">
-        <v>46144.625</v>
+        <v>46144.375</v>
       </c>
       <c r="E393">
         <v>94091</v>
@@ -59425,7 +59425,7 @@
         <v>46144.3751633912</v>
       </c>
       <c r="D394" s="1">
-        <v>46144.62510416667</v>
+        <v>46144.37510416667</v>
       </c>
       <c r="E394">
         <v>94220</v>
@@ -59568,7 +59568,7 @@
         <v>46144.37536819444</v>
       </c>
       <c r="D395" s="1">
-        <v>46144.62534722222</v>
+        <v>46144.37534722222</v>
       </c>
       <c r="E395">
         <v>94625</v>
@@ -59711,7 +59711,7 @@
         <v>46144.375484027776</v>
       </c>
       <c r="D396" s="1">
-        <v>46144.625451388885</v>
+        <v>46144.375451388885</v>
       </c>
       <c r="E396">
         <v>94758</v>
@@ -59854,7 +59854,7 @@
         <v>46144.37560803241</v>
       </c>
       <c r="D397" s="1">
-        <v>46144.62559027778</v>
+        <v>46144.37559027778</v>
       </c>
       <c r="E397">
         <v>94930</v>
@@ -59976,7 +59976,7 @@
         <v>46144.37571493055</v>
       </c>
       <c r="D398" s="1">
-        <v>46144.62569444445</v>
+        <v>46144.37569444445</v>
       </c>
       <c r="E398">
         <v>95166</v>
@@ -60119,7 +60119,7 @@
         <v>46144.37585846065</v>
       </c>
       <c r="D399" s="1">
-        <v>46144.62579861111</v>
+        <v>46144.37579861111</v>
       </c>
       <c r="E399">
         <v>95307</v>
@@ -60262,7 +60262,7 @@
         <v>46144.375956006945</v>
       </c>
       <c r="D400" s="1">
-        <v>46144.6259375</v>
+        <v>46144.3759375</v>
       </c>
       <c r="E400">
         <v>95475</v>
@@ -60384,7 +60384,7 @@
         <v>46144.376062256946</v>
       </c>
       <c r="D401" s="1">
-        <v>46144.62604166667</v>
+        <v>46144.37604166667</v>
       </c>
       <c r="E401">
         <v>95699</v>
@@ -60527,7 +60527,7 @@
         <v>46144.37617658565</v>
       </c>
       <c r="D402" s="1">
-        <v>46144.62614583333</v>
+        <v>46144.37614583333</v>
       </c>
       <c r="E402">
         <v>95836</v>
@@ -60670,7 +60670,7 @@
         <v>46144.37630366898</v>
       </c>
       <c r="D403" s="1">
-        <v>46144.626284722224</v>
+        <v>46144.376284722224</v>
       </c>
       <c r="E403">
         <v>96009</v>
@@ -60792,7 +60792,7 @@
         <v>46144.37640965278</v>
       </c>
       <c r="D404" s="1">
-        <v>46144.626388888886</v>
+        <v>46144.376388888886</v>
       </c>
       <c r="E404">
         <v>96230</v>
@@ -60935,7 +60935,7 @@
         <v>46144.3765525</v>
       </c>
       <c r="D405" s="1">
-        <v>46144.626493055555</v>
+        <v>46144.376493055555</v>
       </c>
       <c r="E405">
         <v>96354</v>
@@ -61078,7 +61078,7 @@
         <v>46144.37675697917</v>
       </c>
       <c r="D406" s="1">
-        <v>46144.62673611111</v>
+        <v>46144.37673611111</v>
       </c>
       <c r="E406">
         <v>96754</v>
@@ -61221,7 +61221,7 @@
         <v>46144.37687136574</v>
       </c>
       <c r="D407" s="1">
-        <v>46144.62684027778</v>
+        <v>46144.37684027778</v>
       </c>
       <c r="E407">
         <v>96881</v>
@@ -61364,7 +61364,7 @@
         <v>46144.376998402775</v>
       </c>
       <c r="D408" s="1">
-        <v>46144.626979166664</v>
+        <v>46144.376979166664</v>
       </c>
       <c r="E408">
         <v>97043</v>
@@ -61486,7 +61486,7 @@
         <v>46144.377103541665</v>
       </c>
       <c r="D409" s="1">
-        <v>46144.62708333333</v>
+        <v>46144.37708333333</v>
       </c>
       <c r="E409">
         <v>97271</v>
@@ -61629,7 +61629,7 @@
         <v>46144.37724663194</v>
       </c>
       <c r="D410" s="1">
-        <v>46144.6271875</v>
+        <v>46144.3771875</v>
       </c>
       <c r="E410">
         <v>97404</v>
@@ -61772,7 +61772,7 @@
         <v>46144.37734432871</v>
       </c>
       <c r="D411" s="1">
-        <v>46144.62732638889</v>
+        <v>46144.37732638889</v>
       </c>
       <c r="E411">
         <v>97578</v>
@@ -61894,7 +61894,7 @@
         <v>46144.37745363426</v>
       </c>
       <c r="D412" s="1">
-        <v>46144.627430555556</v>
+        <v>46144.377430555556</v>
       </c>
       <c r="E412">
         <v>97809</v>
@@ -62037,7 +62037,7 @@
         <v>46144.37756572917</v>
       </c>
       <c r="D413" s="1">
-        <v>46144.627534722225</v>
+        <v>46144.377534722225</v>
       </c>
       <c r="E413">
         <v>97940</v>
@@ -62180,7 +62180,7 @@
         <v>46144.377693090275</v>
       </c>
       <c r="D414" s="1">
-        <v>46144.62767361111</v>
+        <v>46144.37767361111</v>
       </c>
       <c r="E414">
         <v>98113</v>
@@ -62302,7 +62302,7 @@
         <v>46144.37779747685</v>
       </c>
       <c r="D415" s="1">
-        <v>46144.62777777778</v>
+        <v>46144.37777777778</v>
       </c>
       <c r="E415">
         <v>98345</v>
@@ -62445,7 +62445,7 @@
         <v>46144.37794196759</v>
       </c>
       <c r="D416" s="1">
-        <v>46144.62788194444</v>
+        <v>46144.37788194444</v>
       </c>
       <c r="E416">
         <v>98467</v>
@@ -62588,7 +62588,7 @@
         <v>46144.37803597222</v>
       </c>
       <c r="D417" s="1">
-        <v>46144.628020833334</v>
+        <v>46144.378020833334</v>
       </c>
       <c r="E417">
         <v>98628</v>
@@ -62710,7 +62710,7 @@
         <v>46144.37814559028</v>
       </c>
       <c r="D418" s="1">
-        <v>46144.628125</v>
+        <v>46144.378125</v>
       </c>
       <c r="E418">
         <v>98845</v>
@@ -62853,7 +62853,7 @@
         <v>46144.37825408565</v>
       </c>
       <c r="D419" s="1">
-        <v>46144.628229166665</v>
+        <v>46144.378229166665</v>
       </c>
       <c r="E419">
         <v>98957</v>
@@ -62996,7 +62996,7 @@
         <v>46144.37838328704</v>
       </c>
       <c r="D420" s="1">
-        <v>46144.62836805556</v>
+        <v>46144.37836805556</v>
       </c>
       <c r="E420">
         <v>99133</v>
@@ -63118,7 +63118,7 @@
         <v>46144.37849200232</v>
       </c>
       <c r="D421" s="1">
-        <v>46144.62847222222</v>
+        <v>46144.37847222222</v>
       </c>
       <c r="E421">
         <v>99364</v>
@@ -63261,7 +63261,7 @@
         <v>46144.378635787034</v>
       </c>
       <c r="D422" s="1">
-        <v>46144.62857638889</v>
+        <v>46144.37857638889</v>
       </c>
       <c r="E422">
         <v>99491</v>
@@ -63404,7 +63404,7 @@
         <v>46144.37873101852</v>
       </c>
       <c r="D423" s="1">
-        <v>46144.62871527778</v>
+        <v>46144.37871527778</v>
       </c>
       <c r="E423">
         <v>99661</v>
@@ -63526,7 +63526,7 @@
         <v>46144.378840185185</v>
       </c>
       <c r="D424" s="1">
-        <v>46144.62881944444</v>
+        <v>46144.37881944444</v>
       </c>
       <c r="E424">
         <v>99899</v>
@@ -63669,7 +63669,7 @@
         <v>46144.37895518519</v>
       </c>
       <c r="D425" s="1">
-        <v>46144.62892361111</v>
+        <v>46144.37892361111</v>
       </c>
       <c r="E425">
         <v>100020</v>
@@ -63812,7 +63812,7 @@
         <v>46144.379078391205</v>
       </c>
       <c r="D426" s="1">
-        <v>46144.6290625</v>
+        <v>46144.3790625</v>
       </c>
       <c r="E426">
         <v>100180</v>
@@ -63934,7 +63934,7 @@
         <v>46144.379186805556</v>
       </c>
       <c r="D427" s="1">
-        <v>46144.629166666666</v>
+        <v>46144.379166666666</v>
       </c>
       <c r="E427">
         <v>100398</v>
@@ -64077,7 +64077,7 @@
         <v>46144.379325625</v>
       </c>
       <c r="D428" s="1">
-        <v>46144.629270833335</v>
+        <v>46144.379270833335</v>
       </c>
       <c r="E428">
         <v>100517</v>
@@ -64220,7 +64220,7 @@
         <v>46144.37942787037</v>
       </c>
       <c r="D429" s="1">
-        <v>46144.62940972222</v>
+        <v>46144.37940972222</v>
       </c>
       <c r="E429">
         <v>100679</v>
@@ -64342,7 +64342,7 @@
         <v>46144.37953398148</v>
       </c>
       <c r="D430" s="1">
-        <v>46144.62951388889</v>
+        <v>46144.37951388889</v>
       </c>
       <c r="E430">
         <v>100896</v>
@@ -64485,7 +64485,7 @@
         <v>46144.379643333334</v>
       </c>
       <c r="D431" s="1">
-        <v>46144.62961805556</v>
+        <v>46144.37961805556</v>
       </c>
       <c r="E431">
         <v>101026</v>
@@ -64628,7 +64628,7 @@
         <v>46144.37977248843</v>
       </c>
       <c r="D432" s="1">
-        <v>46144.62975694444</v>
+        <v>46144.37975694444</v>
       </c>
       <c r="E432">
         <v>101187</v>
@@ -64750,7 +64750,7 @@
         <v>46144.379881354165</v>
       </c>
       <c r="D433" s="1">
-        <v>46144.62986111111</v>
+        <v>46144.37986111111</v>
       </c>
       <c r="E433">
         <v>101407</v>
@@ -64893,7 +64893,7 @@
         <v>46144.38002553241</v>
       </c>
       <c r="D434" s="1">
-        <v>46144.629965277774</v>
+        <v>46144.379965277774</v>
       </c>
       <c r="E434">
         <v>101531</v>
@@ -65036,7 +65036,7 @@
         <v>46144.38012429398</v>
       </c>
       <c r="D435" s="1">
-        <v>46144.63010416667</v>
+        <v>46144.38010416667</v>
       </c>
       <c r="E435">
         <v>101696</v>
@@ -65158,7 +65158,7 @@
         <v>46144.38023047454</v>
       </c>
       <c r="D436" s="1">
-        <v>46144.630208333336</v>
+        <v>46144.380208333336</v>
       </c>
       <c r="E436">
         <v>101917</v>
@@ -65301,7 +65301,7 @@
         <v>46144.38034398148</v>
       </c>
       <c r="D437" s="1">
-        <v>46144.6303125</v>
+        <v>46144.3803125</v>
       </c>
       <c r="E437">
         <v>102026</v>
@@ -65444,7 +65444,7 @@
         <v>46144.3804859375</v>
       </c>
       <c r="D438" s="1">
-        <v>46144.63045138889</v>
+        <v>46144.38045138889</v>
       </c>
       <c r="E438">
         <v>102195</v>
@@ -65566,7 +65566,7 @@
         <v>46144.38057616898</v>
       </c>
       <c r="D439" s="1">
-        <v>46144.63055555556</v>
+        <v>46144.38055555556</v>
       </c>
       <c r="E439">
         <v>102428</v>
@@ -65709,7 +65709,7 @@
         <v>46144.38072216435</v>
       </c>
       <c r="D440" s="1">
-        <v>46144.63065972222</v>
+        <v>46144.38065972222</v>
       </c>
       <c r="E440">
         <v>102549</v>
@@ -65852,7 +65852,7 @@
         <v>46144.38081400463</v>
       </c>
       <c r="D441" s="1">
-        <v>46144.63079861111</v>
+        <v>46144.38079861111</v>
       </c>
       <c r="E441">
         <v>102693</v>
@@ -65974,7 +65974,7 @@
         <v>46144.380922847224</v>
       </c>
       <c r="D442" s="1">
-        <v>46144.630902777775</v>
+        <v>46144.380902777775</v>
       </c>
       <c r="E442">
         <v>102916</v>
@@ -66117,7 +66117,7 @@
         <v>46144.3810381713</v>
       </c>
       <c r="D443" s="1">
-        <v>46144.631006944444</v>
+        <v>46144.381006944444</v>
       </c>
       <c r="E443">
         <v>103030</v>
@@ -66260,7 +66260,7 @@
         <v>46144.38116185185</v>
       </c>
       <c r="D444" s="1">
-        <v>46144.63114583334</v>
+        <v>46144.38114583334</v>
       </c>
       <c r="E444">
         <v>103185</v>
@@ -66382,7 +66382,7 @@
         <v>46144.3812702662</v>
       </c>
       <c r="D445" s="1">
-        <v>46144.63125</v>
+        <v>46144.38125</v>
       </c>
       <c r="E445">
         <v>103416</v>
@@ -66525,7 +66525,7 @@
         <v>46144.38141414352</v>
       </c>
       <c r="D446" s="1">
-        <v>46144.63135416667</v>
+        <v>46144.38135416667</v>
       </c>
       <c r="E446">
         <v>103517</v>
@@ -66668,7 +66668,7 @@
         <v>46144.38150966435</v>
       </c>
       <c r="D447" s="1">
-        <v>46144.63149305555</v>
+        <v>46144.38149305555</v>
       </c>
       <c r="E447">
         <v>103668</v>
@@ -66790,7 +66790,7 @@
         <v>46144.38161707176</v>
       </c>
       <c r="D448" s="1">
-        <v>46144.63159722222</v>
+        <v>46144.38159722222</v>
       </c>
       <c r="E448">
         <v>103891</v>
@@ -66933,7 +66933,7 @@
         <v>46144.381731932874</v>
       </c>
       <c r="D449" s="1">
-        <v>46144.63170138889</v>
+        <v>46144.38170138889</v>
       </c>
       <c r="E449">
         <v>103989</v>
@@ -67076,7 +67076,7 @@
         <v>46144.38185494213</v>
       </c>
       <c r="D450" s="1">
-        <v>46144.631840277776</v>
+        <v>46144.381840277776</v>
       </c>
       <c r="E450">
         <v>104130</v>
@@ -67198,7 +67198,7 @@
         <v>46144.38196471065</v>
       </c>
       <c r="D451" s="1">
-        <v>46144.631944444445</v>
+        <v>46144.381944444445</v>
       </c>
       <c r="E451">
         <v>104342</v>
@@ -67341,7 +67341,7 @@
         <v>46144.38210259259</v>
       </c>
       <c r="D452" s="1">
-        <v>46144.632048611114</v>
+        <v>46144.382048611114</v>
       </c>
       <c r="E452">
         <v>104441</v>
@@ -67484,7 +67484,7 @@
         <v>46144.382202430555</v>
       </c>
       <c r="D453" s="1">
-        <v>46144.6321875</v>
+        <v>46144.3821875</v>
       </c>
       <c r="E453">
         <v>104587</v>
@@ -67606,7 +67606,7 @@
         <v>46144.38231193287</v>
       </c>
       <c r="D454" s="1">
-        <v>46144.63229166667</v>
+        <v>46144.38229166667</v>
       </c>
       <c r="E454">
         <v>104797</v>
@@ -67749,7 +67749,7 @@
         <v>46144.38242115741</v>
       </c>
       <c r="D455" s="1">
-        <v>46144.63239583333</v>
+        <v>46144.38239583333</v>
       </c>
       <c r="E455">
         <v>104895</v>
@@ -67892,7 +67892,7 @@
         <v>46144.38255054398</v>
       </c>
       <c r="D456" s="1">
-        <v>46144.63253472222</v>
+        <v>46144.38253472222</v>
       </c>
       <c r="E456">
         <v>105036</v>
@@ -68014,7 +68014,7 @@
         <v>46144.38265883102</v>
       </c>
       <c r="D457" s="1">
-        <v>46144.63263888889</v>
+        <v>46144.38263888889</v>
       </c>
       <c r="E457">
         <v>105248</v>
@@ -68157,7 +68157,7 @@
         <v>46144.38279736111</v>
       </c>
       <c r="D458" s="1">
-        <v>46144.632743055554</v>
+        <v>46144.382743055554</v>
       </c>
       <c r="E458">
         <v>105357</v>
@@ -68300,7 +68300,7 @@
         <v>46144.38289775463</v>
       </c>
       <c r="D459" s="1">
-        <v>46144.632881944446</v>
+        <v>46144.382881944446</v>
       </c>
       <c r="E459">
         <v>105489</v>
@@ -68422,7 +68422,7 @@
         <v>46144.38300627315</v>
       </c>
       <c r="D460" s="1">
-        <v>46144.63298611111</v>
+        <v>46144.38298611111</v>
       </c>
       <c r="E460">
         <v>105660</v>
@@ -68565,7 +68565,7 @@
         <v>46144.383115358796</v>
       </c>
       <c r="D461" s="1">
-        <v>46144.63309027778</v>
+        <v>46144.38309027778</v>
       </c>
       <c r="E461">
         <v>105799</v>
@@ -68708,7 +68708,7 @@
         <v>46144.3832456713</v>
       </c>
       <c r="D462" s="1">
-        <v>46144.63322916667</v>
+        <v>46144.38322916667</v>
       </c>
       <c r="E462">
         <v>105938</v>
@@ -68830,7 +68830,7 @@
         <v>46144.383353460646</v>
       </c>
       <c r="D463" s="1">
-        <v>46144.63333333333</v>
+        <v>46144.38333333333</v>
       </c>
       <c r="E463">
         <v>106139</v>
@@ -68973,7 +68973,7 @@
         <v>46144.38349201389</v>
       </c>
       <c r="D464" s="1">
-        <v>46144.6334375</v>
+        <v>46144.3834375</v>
       </c>
       <c r="E464">
         <v>106253</v>
@@ -69116,7 +69116,7 @@
         <v>46144.383615520834</v>
       </c>
       <c r="D465" s="1">
-        <v>46144.63359953704</v>
+        <v>46144.38359953704</v>
       </c>
       <c r="E465">
         <v>106421</v>
@@ -69238,7 +69238,7 @@
         <v>46144.383701597224</v>
       </c>
       <c r="D466" s="1">
-        <v>46144.633680555555</v>
+        <v>46144.383680555555</v>
       </c>
       <c r="E466">
         <v>106597</v>
@@ -69381,7 +69381,7 @@
         <v>46144.383810046296</v>
       </c>
       <c r="D467" s="1">
-        <v>46144.633784722224</v>
+        <v>46144.383784722224</v>
       </c>
       <c r="E467">
         <v>106701</v>
@@ -69524,7 +69524,7 @@
         <v>46144.38396331018</v>
       </c>
       <c r="D468" s="1">
-        <v>46144.63394675926</v>
+        <v>46144.38394675926</v>
       </c>
       <c r="E468">
         <v>106864</v>
@@ -69646,7 +69646,7 @@
         <v>46144.384047997686</v>
       </c>
       <c r="D469" s="1">
-        <v>46144.63402777778</v>
+        <v>46144.38402777778</v>
       </c>
       <c r="E469">
         <v>107044</v>
@@ -69945,7 +69945,7 @@
         <v>46144.384321805555</v>
       </c>
       <c r="D2" s="1">
-        <v>46144.634305555555</v>
+        <v>46144.384305555555</v>
       </c>
       <c r="E2">
         <v>106703</v>
@@ -70031,7 +70031,7 @@
         <v>46144.3844044213</v>
       </c>
       <c r="D3" s="1">
-        <v>46144.634375</v>
+        <v>46144.384375</v>
       </c>
       <c r="E3">
         <v>105648</v>
@@ -70162,7 +70162,7 @@
         <v>46144.38450599537</v>
       </c>
       <c r="D4" s="1">
-        <v>46144.63447916666</v>
+        <v>46144.38447916666</v>
       </c>
       <c r="E4">
         <v>104197</v>
@@ -70305,7 +70305,7 @@
         <v>46144.38467046296</v>
       </c>
       <c r="D5" s="1">
-        <v>46144.63465277778</v>
+        <v>46144.38465277778</v>
       </c>
       <c r="E5">
         <v>101932</v>
@@ -70427,7 +70427,7 @@
         <v>46144.38474241898</v>
       </c>
       <c r="D6" s="1">
-        <v>46144.634722222225</v>
+        <v>46144.384722222225</v>
       </c>
       <c r="E6">
         <v>100903</v>
@@ -70570,7 +70570,7 @@
         <v>46144.38503922454</v>
       </c>
       <c r="D7" s="1">
-        <v>46144.63502314815</v>
+        <v>46144.38502314815</v>
       </c>
       <c r="E7">
         <v>97266</v>
@@ -70692,7 +70692,7 @@
         <v>46144.38508954861</v>
       </c>
       <c r="D8" s="1">
-        <v>46144.63506944444</v>
+        <v>46144.38506944444</v>
       </c>
       <c r="E8">
         <v>96698</v>
@@ -70835,7 +70835,7 @@
         <v>46144.385200578705</v>
       </c>
       <c r="D9" s="1">
-        <v>46144.63517361111</v>
+        <v>46144.38517361111</v>
       </c>
       <c r="E9">
         <v>95568</v>
@@ -70978,7 +70978,7 @@
         <v>46144.38538491898</v>
       </c>
       <c r="D10" s="1">
-        <v>46144.63537037037</v>
+        <v>46144.38537037037</v>
       </c>
       <c r="E10">
         <v>93663</v>
@@ -71100,7 +71100,7 @@
         <v>46144.38543696759</v>
       </c>
       <c r="D11" s="1">
-        <v>46144.635416666664</v>
+        <v>46144.385416666664</v>
       </c>
       <c r="E11">
         <v>93115</v>
@@ -71243,7 +71243,7 @@
         <v>46144.38557668981</v>
       </c>
       <c r="D12" s="1">
-        <v>46144.63552083333</v>
+        <v>46144.38552083333</v>
       </c>
       <c r="E12">
         <v>92061</v>
@@ -71386,7 +71386,7 @@
         <v>46144.385733333336</v>
       </c>
       <c r="D13" s="1">
-        <v>46144.635717592595</v>
+        <v>46144.385717592595</v>
       </c>
       <c r="E13">
         <v>90359</v>
@@ -71508,7 +71508,7 @@
         <v>46144.38578493056</v>
       </c>
       <c r="D14" s="1">
-        <v>46144.63576388889</v>
+        <v>46144.38576388889</v>
       </c>
       <c r="E14">
         <v>89853</v>
@@ -71651,7 +71651,7 @@
         <v>46144.38589548611</v>
       </c>
       <c r="D15" s="1">
-        <v>46144.63586805556</v>
+        <v>46144.38586805556</v>
       </c>
       <c r="E15">
         <v>88875</v>
@@ -71794,7 +71794,7 @@
         <v>46144.38607988426</v>
       </c>
       <c r="D16" s="1">
-        <v>46144.63606481482</v>
+        <v>46144.38606481482</v>
       </c>
       <c r="E16">
         <v>87209</v>
@@ -71916,7 +71916,7 @@
         <v>46144.38613212963</v>
       </c>
       <c r="D17" s="1">
-        <v>46144.63611111111</v>
+        <v>46144.38611111111</v>
       </c>
       <c r="E17">
         <v>86743</v>
@@ -72059,7 +72059,7 @@
         <v>46144.38627113426</v>
       </c>
       <c r="D18" s="1">
-        <v>46144.63621527778</v>
+        <v>46144.38621527778</v>
       </c>
       <c r="E18">
         <v>85853</v>
@@ -72202,7 +72202,7 @@
         <v>46144.38642780093</v>
       </c>
       <c r="D19" s="1">
-        <v>46144.636412037034</v>
+        <v>46144.386412037034</v>
       </c>
       <c r="E19">
         <v>84423</v>
@@ -72324,7 +72324,7 @@
         <v>46144.386480810186</v>
       </c>
       <c r="D20" s="1">
-        <v>46144.636458333334</v>
+        <v>46144.386458333334</v>
       </c>
       <c r="E20">
         <v>83986</v>
@@ -72467,7 +72467,7 @@
         <v>46144.38658846065</v>
       </c>
       <c r="D21" s="1">
-        <v>46144.6365625</v>
+        <v>46144.3865625</v>
       </c>
       <c r="E21">
         <v>83139</v>
@@ -72610,7 +72610,7 @@
         <v>46144.38677424769</v>
       </c>
       <c r="D22" s="1">
-        <v>46144.63675925926</v>
+        <v>46144.38675925926</v>
       </c>
       <c r="E22">
         <v>81670</v>
@@ -72732,7 +72732,7 @@
         <v>46144.386825960646</v>
       </c>
       <c r="D23" s="1">
-        <v>46144.63680555556</v>
+        <v>46144.38680555556</v>
       </c>
       <c r="E23">
         <v>81312</v>
@@ -72875,7 +72875,7 @@
         <v>46144.386966238424</v>
       </c>
       <c r="D24" s="1">
-        <v>46144.63690972222</v>
+        <v>46144.38690972222</v>
       </c>
       <c r="E24">
         <v>80570</v>
@@ -73018,7 +73018,7 @@
         <v>46144.3871221875</v>
       </c>
       <c r="D25" s="1">
-        <v>46144.63710648148</v>
+        <v>46144.38710648148</v>
       </c>
       <c r="E25">
         <v>79216</v>
@@ -73140,7 +73140,7 @@
         <v>46144.387174166666</v>
       </c>
       <c r="D26" s="1">
-        <v>46144.63715277778</v>
+        <v>46144.38715277778</v>
       </c>
       <c r="E26">
         <v>78836</v>
@@ -73283,7 +73283,7 @@
         <v>46144.38728337963</v>
       </c>
       <c r="D27" s="1">
-        <v>46144.63725694444</v>
+        <v>46144.38725694444</v>
       </c>
       <c r="E27">
         <v>78056</v>
@@ -73426,7 +73426,7 @@
         <v>46144.38746997685</v>
       </c>
       <c r="D28" s="1">
-        <v>46144.637453703705</v>
+        <v>46144.387453703705</v>
       </c>
       <c r="E28">
         <v>76821</v>
@@ -73548,7 +73548,7 @@
         <v>46144.387519641205</v>
       </c>
       <c r="D29" s="1">
-        <v>46144.6375</v>
+        <v>46144.3875</v>
       </c>
       <c r="E29">
         <v>76472</v>
@@ -73691,7 +73691,7 @@
         <v>46144.38766013889</v>
       </c>
       <c r="D30" s="1">
-        <v>46144.637604166666</v>
+        <v>46144.387604166666</v>
       </c>
       <c r="E30">
         <v>75730</v>
@@ -73834,7 +73834,7 @@
         <v>46144.38782887731</v>
       </c>
       <c r="D31" s="1">
-        <v>46144.6378125</v>
+        <v>46144.3878125</v>
       </c>
       <c r="E31">
         <v>74507</v>
@@ -73956,7 +73956,7 @@
         <v>46144.38786804398</v>
       </c>
       <c r="D32" s="1">
-        <v>46144.63784722222</v>
+        <v>46144.38784722222</v>
       </c>
       <c r="E32">
         <v>74293</v>
@@ -74099,7 +74099,7 @@
         <v>46144.38797862268</v>
       </c>
       <c r="D33" s="1">
-        <v>46144.63795138889</v>
+        <v>46144.38795138889</v>
       </c>
       <c r="E33">
         <v>73629</v>
@@ -74242,7 +74242,7 @@
         <v>46144.38817590278</v>
       </c>
       <c r="D34" s="1">
-        <v>46144.63815972222</v>
+        <v>46144.38815972222</v>
       </c>
       <c r="E34">
         <v>72424</v>
@@ -74364,7 +74364,7 @@
         <v>46144.38821445602</v>
       </c>
       <c r="D35" s="1">
-        <v>46144.638194444444</v>
+        <v>46144.388194444444</v>
       </c>
       <c r="E35">
         <v>72216</v>
@@ -74507,7 +74507,7 @@
         <v>46144.38835627315</v>
       </c>
       <c r="D36" s="1">
-        <v>46144.63829861111</v>
+        <v>46144.38829861111</v>
       </c>
       <c r="E36">
         <v>71586</v>
@@ -74650,7 +74650,7 @@
         <v>46144.388523125</v>
       </c>
       <c r="D37" s="1">
-        <v>46144.638506944444</v>
+        <v>46144.388506944444</v>
       </c>
       <c r="E37">
         <v>70416</v>
@@ -74772,7 +74772,7 @@
         <v>46144.388561747684</v>
       </c>
       <c r="D38" s="1">
-        <v>46144.63854166667</v>
+        <v>46144.38854166667</v>
       </c>
       <c r="E38">
         <v>70166</v>
@@ -74915,7 +74915,7 @@
         <v>46144.38867357639</v>
       </c>
       <c r="D39" s="1">
-        <v>46144.638645833336</v>
+        <v>46144.388645833336</v>
       </c>
       <c r="E39">
         <v>69534</v>
@@ -75058,7 +75058,7 @@
         <v>46144.388870358795</v>
       </c>
       <c r="D40" s="1">
-        <v>46144.63885416667</v>
+        <v>46144.38885416667</v>
       </c>
       <c r="E40">
         <v>68365</v>
@@ -75180,7 +75180,7 @@
         <v>46144.38890893519</v>
       </c>
       <c r="D41" s="1">
-        <v>46144.63888888889</v>
+        <v>46144.38888888889</v>
       </c>
       <c r="E41">
         <v>68165</v>
@@ -75323,7 +75323,7 @@
         <v>46144.38905232639</v>
       </c>
       <c r="D42" s="1">
-        <v>46144.63899305555</v>
+        <v>46144.38899305555</v>
       </c>
       <c r="E42">
         <v>67559</v>
@@ -75466,7 +75466,7 @@
         <v>46144.38921686343</v>
       </c>
       <c r="D43" s="1">
-        <v>46144.63920138889</v>
+        <v>46144.38920138889</v>
       </c>
       <c r="E43">
         <v>66468</v>
@@ -75588,7 +75588,7 @@
         <v>46144.38925619213</v>
       </c>
       <c r="D44" s="1">
-        <v>46144.639236111114</v>
+        <v>46144.389236111114</v>
       </c>
       <c r="E44">
         <v>66267</v>
@@ -75731,7 +75731,7 @@
         <v>46144.38936851852</v>
       </c>
       <c r="D45" s="1">
-        <v>46144.639340277776</v>
+        <v>46144.389340277776</v>
       </c>
       <c r="E45">
         <v>65703</v>
@@ -75874,7 +75874,7 @@
         <v>46144.38956405093</v>
       </c>
       <c r="D46" s="1">
-        <v>46144.639548611114</v>
+        <v>46144.389548611114</v>
       </c>
       <c r="E46">
         <v>64739</v>
@@ -75996,7 +75996,7 @@
         <v>46144.38960383102</v>
       </c>
       <c r="D47" s="1">
-        <v>46144.63958333333</v>
+        <v>46144.38958333333</v>
       </c>
       <c r="E47">
         <v>64597</v>
@@ -76139,7 +76139,7 @@
         <v>46144.38974532407</v>
       </c>
       <c r="D48" s="1">
-        <v>46144.6396875</v>
+        <v>46144.3896875</v>
       </c>
       <c r="E48">
         <v>64080</v>
@@ -76282,7 +76282,7 @@
         <v>46144.389912164355</v>
       </c>
       <c r="D49" s="1">
-        <v>46144.63989583333</v>
+        <v>46144.38989583333</v>
       </c>
       <c r="E49">
         <v>63095</v>
@@ -76404,7 +76404,7 @@
         <v>46144.38995091435</v>
       </c>
       <c r="D50" s="1">
-        <v>46144.63993055555</v>
+        <v>46144.38993055555</v>
       </c>
       <c r="E50">
         <v>62940</v>
@@ -76547,7 +76547,7 @@
         <v>46144.39006480324</v>
       </c>
       <c r="D51" s="1">
-        <v>46144.64003472222</v>
+        <v>46144.39003472222</v>
       </c>
       <c r="E51">
         <v>62432</v>
@@ -76690,7 +76690,7 @@
         <v>46144.390259155094</v>
       </c>
       <c r="D52" s="1">
-        <v>46144.64024305555</v>
+        <v>46144.39024305555</v>
       </c>
       <c r="E52">
         <v>61491</v>
@@ -76812,7 +76812,7 @@
         <v>46144.390297962964</v>
       </c>
       <c r="D53" s="1">
-        <v>46144.64027777778</v>
+        <v>46144.39027777778</v>
       </c>
       <c r="E53">
         <v>61350</v>
@@ -76955,7 +76955,7 @@
         <v>46144.390439814815</v>
       </c>
       <c r="D54" s="1">
-        <v>46144.640381944446</v>
+        <v>46144.390381944446</v>
       </c>
       <c r="E54">
         <v>60906</v>
@@ -77098,7 +77098,7 @@
         <v>46144.39060578703</v>
       </c>
       <c r="D55" s="1">
-        <v>46144.64059027778</v>
+        <v>46144.39059027778</v>
       </c>
       <c r="E55">
         <v>60080</v>
@@ -77220,7 +77220,7 @@
         <v>46144.39064547454</v>
       </c>
       <c r="D56" s="1">
-        <v>46144.640625</v>
+        <v>46144.390625</v>
       </c>
       <c r="E56">
         <v>59918</v>
@@ -77363,7 +77363,7 @@
         <v>46144.39075974537</v>
       </c>
       <c r="D57" s="1">
-        <v>46144.64072916667</v>
+        <v>46144.39072916667</v>
       </c>
       <c r="E57">
         <v>59441</v>
@@ -77506,7 +77506,7 @@
         <v>46144.390953483795</v>
       </c>
       <c r="D58" s="1">
-        <v>46144.6409375</v>
+        <v>46144.3909375</v>
       </c>
       <c r="E58">
         <v>58600</v>
@@ -77628,7 +77628,7 @@
         <v>46144.3909925</v>
       </c>
       <c r="D59" s="1">
-        <v>46144.64097222222</v>
+        <v>46144.39097222222</v>
       </c>
       <c r="E59">
         <v>58467</v>
@@ -77771,7 +77771,7 @@
         <v>46144.39113372685</v>
       </c>
       <c r="D60" s="1">
-        <v>46144.641076388885</v>
+        <v>46144.391076388885</v>
       </c>
       <c r="E60">
         <v>58029</v>
@@ -77914,7 +77914,7 @@
         <v>46144.39130177083</v>
       </c>
       <c r="D61" s="1">
-        <v>46144.641284722224</v>
+        <v>46144.391284722224</v>
       </c>
       <c r="E61">
         <v>57251</v>
@@ -78036,7 +78036,7 @@
         <v>46144.39133958334</v>
       </c>
       <c r="D62" s="1">
-        <v>46144.64131944445</v>
+        <v>46144.39131944445</v>
       </c>
       <c r="E62">
         <v>57131</v>
@@ -78179,7 +78179,7 @@
         <v>46144.39145206018</v>
       </c>
       <c r="D63" s="1">
-        <v>46144.64142361111</v>
+        <v>46144.39142361111</v>
       </c>
       <c r="E63">
         <v>56716</v>
@@ -78322,7 +78322,7 @@
         <v>46144.39164814815</v>
       </c>
       <c r="D64" s="1">
-        <v>46144.64163194445</v>
+        <v>46144.39163194445</v>
       </c>
       <c r="E64">
         <v>55962</v>
@@ -78444,7 +78444,7 @@
         <v>46144.39168642361</v>
       </c>
       <c r="D65" s="1">
-        <v>46144.64166666667</v>
+        <v>46144.39166666667</v>
       </c>
       <c r="E65">
         <v>55855</v>
@@ -78587,7 +78587,7 @@
         <v>46144.391828182874</v>
       </c>
       <c r="D66" s="1">
-        <v>46144.64177083333</v>
+        <v>46144.39177083333</v>
       </c>
       <c r="E66">
         <v>55443</v>
@@ -78730,7 +78730,7 @@
         <v>46144.39199400463</v>
       </c>
       <c r="D67" s="1">
-        <v>46144.64197916666</v>
+        <v>46144.39197916666</v>
       </c>
       <c r="E67">
         <v>54735</v>
@@ -78852,7 +78852,7 @@
         <v>46144.39203474537</v>
       </c>
       <c r="D68" s="1">
-        <v>46144.642013888886</v>
+        <v>46144.392013888886</v>
       </c>
       <c r="E68">
         <v>54635</v>
@@ -78995,7 +78995,7 @@
         <v>46144.392146701386</v>
       </c>
       <c r="D69" s="1">
-        <v>46144.642118055555</v>
+        <v>46144.392118055555</v>
       </c>
       <c r="E69">
         <v>54258</v>
@@ -79138,7 +79138,7 @@
         <v>46144.392342708335</v>
       </c>
       <c r="D70" s="1">
-        <v>46144.64232638889</v>
+        <v>46144.39232638889</v>
       </c>
       <c r="E70">
         <v>53557</v>
@@ -79260,7 +79260,7 @@
         <v>46144.39238321759</v>
       </c>
       <c r="D71" s="1">
-        <v>46144.64236111111</v>
+        <v>46144.39236111111</v>
       </c>
       <c r="E71">
         <v>53466</v>
@@ -79403,7 +79403,7 @@
         <v>46144.392522905095</v>
       </c>
       <c r="D72" s="1">
-        <v>46144.64246527778</v>
+        <v>46144.39246527778</v>
       </c>
       <c r="E72">
         <v>53100</v>
@@ -79546,7 +79546,7 @@
         <v>46144.3926908912</v>
       </c>
       <c r="D73" s="1">
-        <v>46144.64267361111</v>
+        <v>46144.39267361111</v>
       </c>
       <c r="E73">
         <v>52431</v>
@@ -79668,7 +79668,7 @@
         <v>46144.3927280787</v>
       </c>
       <c r="D74" s="1">
-        <v>46144.64270833333</v>
+        <v>46144.39270833333</v>
       </c>
       <c r="E74">
         <v>52340</v>
@@ -79811,7 +79811,7 @@
         <v>46144.39284247685</v>
       </c>
       <c r="D75" s="1">
-        <v>46144.6428125</v>
+        <v>46144.3928125</v>
       </c>
       <c r="E75">
         <v>51981</v>
@@ -79954,7 +79954,7 @@
         <v>46144.39303627315</v>
       </c>
       <c r="D76" s="1">
-        <v>46144.64302083333</v>
+        <v>46144.39302083333</v>
       </c>
       <c r="E76">
         <v>51322</v>
@@ -80076,7 +80076,7 @@
         <v>46144.39307614583</v>
       </c>
       <c r="D77" s="1">
-        <v>46144.643055555556</v>
+        <v>46144.393055555556</v>
       </c>
       <c r="E77">
         <v>51241</v>
@@ -80219,7 +80219,7 @@
         <v>46144.393217557874</v>
       </c>
       <c r="D78" s="1">
-        <v>46144.643159722225</v>
+        <v>46144.393159722225</v>
       </c>
       <c r="E78">
         <v>50882</v>
@@ -80362,7 +80362,7 @@
         <v>46144.39338446759</v>
       </c>
       <c r="D79" s="1">
-        <v>46144.64336805556</v>
+        <v>46144.39336805556</v>
       </c>
       <c r="E79">
         <v>50256</v>
@@ -80484,7 +80484,7 @@
         <v>46144.393423738424</v>
       </c>
       <c r="D80" s="1">
-        <v>46144.64340277778</v>
+        <v>46144.39340277778</v>
       </c>
       <c r="E80">
         <v>50188</v>
@@ -80627,7 +80627,7 @@
         <v>46144.393535497686</v>
       </c>
       <c r="D81" s="1">
-        <v>46144.64350694444</v>
+        <v>46144.39350694444</v>
       </c>
       <c r="E81">
         <v>49834</v>
@@ -80770,7 +80770,7 @@
         <v>46144.393731550925</v>
       </c>
       <c r="D82" s="1">
-        <v>46144.64371527778</v>
+        <v>46144.39371527778</v>
       </c>
       <c r="E82">
         <v>49225</v>
@@ -80892,7 +80892,7 @@
         <v>46144.393770636576</v>
       </c>
       <c r="D83" s="1">
-        <v>46144.64375</v>
+        <v>46144.39375</v>
       </c>
       <c r="E83">
         <v>49153</v>
@@ -81035,7 +81035,7 @@
         <v>46144.3939121875</v>
       </c>
       <c r="D84" s="1">
-        <v>46144.643854166665</v>
+        <v>46144.393854166665</v>
       </c>
       <c r="E84">
         <v>48809</v>
@@ -81178,7 +81178,7 @@
         <v>46144.394080555554</v>
       </c>
       <c r="D85" s="1">
-        <v>46144.6440625</v>
+        <v>46144.3940625</v>
       </c>
       <c r="E85">
         <v>48208</v>
@@ -81300,7 +81300,7 @@
         <v>46144.394117881944</v>
       </c>
       <c r="D86" s="1">
-        <v>46144.64409722222</v>
+        <v>46144.39409722222</v>
       </c>
       <c r="E86">
         <v>48136</v>
@@ -81443,7 +81443,7 @@
         <v>46144.39423017361</v>
       </c>
       <c r="D87" s="1">
-        <v>46144.64420138889</v>
+        <v>46144.39420138889</v>
       </c>
       <c r="E87">
         <v>47808</v>
@@ -81586,7 +81586,7 @@
         <v>46144.394426782404</v>
       </c>
       <c r="D88" s="1">
-        <v>46144.64440972222</v>
+        <v>46144.39440972222</v>
       </c>
       <c r="E88">
         <v>47201</v>
@@ -81708,7 +81708,7 @@
         <v>46144.394464641206</v>
       </c>
       <c r="D89" s="1">
-        <v>46144.64444444444</v>
+        <v>46144.39444444444</v>
       </c>
       <c r="E89">
         <v>47116</v>
@@ -81851,7 +81851,7 @@
         <v>46144.394608807874</v>
       </c>
       <c r="D90" s="1">
-        <v>46144.64454861111</v>
+        <v>46144.39454861111</v>
       </c>
       <c r="E90">
         <v>46796</v>
@@ -81994,7 +81994,7 @@
         <v>46144.394772719905</v>
       </c>
       <c r="D91" s="1">
-        <v>46144.64475694444</v>
+        <v>46144.39475694444</v>
       </c>
       <c r="E91">
         <v>46203</v>
@@ -82116,7 +82116,7 @@
         <v>46144.39481197917</v>
       </c>
       <c r="D92" s="1">
-        <v>46144.644791666666</v>
+        <v>46144.394791666666</v>
       </c>
       <c r="E92">
         <v>46138</v>
@@ -82259,7 +82259,7 @@
         <v>46144.3949259375</v>
       </c>
       <c r="D93" s="1">
-        <v>46144.644895833335</v>
+        <v>46144.394895833335</v>
       </c>
       <c r="E93">
         <v>45826</v>
@@ -82402,7 +82402,7 @@
         <v>46144.39512039352</v>
       </c>
       <c r="D94" s="1">
-        <v>46144.645104166666</v>
+        <v>46144.395104166666</v>
       </c>
       <c r="E94">
         <v>45265</v>
@@ -82524,7 +82524,7 @@
         <v>46144.39515946759</v>
       </c>
       <c r="D95" s="1">
-        <v>46144.64513888889</v>
+        <v>46144.39513888889</v>
       </c>
       <c r="E95">
         <v>45204</v>
@@ -82667,7 +82667,7 @@
         <v>46144.395301041666</v>
       </c>
       <c r="D96" s="1">
-        <v>46144.64524305556</v>
+        <v>46144.39524305556</v>
       </c>
       <c r="E96">
         <v>44892</v>
@@ -82810,7 +82810,7 @@
         <v>46144.39546821759</v>
       </c>
       <c r="D97" s="1">
-        <v>46144.64545138889</v>
+        <v>46144.39545138889</v>
       </c>
       <c r="E97">
         <v>44284</v>
@@ -82932,7 +82932,7 @@
         <v>46144.395506493056</v>
       </c>
       <c r="D98" s="1">
-        <v>46144.64548611111</v>
+        <v>46144.39548611111</v>
       </c>
       <c r="E98">
         <v>44234</v>
@@ -83075,7 +83075,7 @@
         <v>46144.39561989583</v>
       </c>
       <c r="D99" s="1">
-        <v>46144.645590277774</v>
+        <v>46144.395590277774</v>
       </c>
       <c r="E99">
         <v>43929</v>
@@ -83218,7 +83218,7 @@
         <v>46144.39581483796</v>
       </c>
       <c r="D100" s="1">
-        <v>46144.64579861111</v>
+        <v>46144.39579861111</v>
       </c>
       <c r="E100">
         <v>43388</v>
@@ -83340,7 +83340,7 @@
         <v>46144.39599557871</v>
       </c>
       <c r="D101" s="1">
-        <v>46144.6459375</v>
+        <v>46144.3959375</v>
       </c>
       <c r="E101">
         <v>43043</v>
@@ -83483,7 +83483,7 @@
         <v>46144.39616212963</v>
       </c>
       <c r="D102" s="1">
-        <v>46144.646145833336</v>
+        <v>46144.396145833336</v>
       </c>
       <c r="E102">
         <v>42522</v>
@@ -83605,7 +83605,7 @@
         <v>46144.39620056713</v>
       </c>
       <c r="D103" s="1">
-        <v>46144.64618055556</v>
+        <v>46144.39618055556</v>
       </c>
       <c r="E103">
         <v>42469</v>
@@ -83748,7 +83748,7 @@
         <v>46144.39631364583</v>
       </c>
       <c r="D104" s="1">
-        <v>46144.64628472222</v>
+        <v>46144.39628472222</v>
       </c>
       <c r="E104">
         <v>42187</v>
@@ -83891,7 +83891,7 @@
         <v>46144.396508275466</v>
       </c>
       <c r="D105" s="1">
-        <v>46144.64649305555</v>
+        <v>46144.39649305555</v>
       </c>
       <c r="E105">
         <v>41685</v>
@@ -84013,7 +84013,7 @@
         <v>46144.396689594905</v>
       </c>
       <c r="D106" s="1">
-        <v>46144.646631944444</v>
+        <v>46144.396631944444</v>
       </c>
       <c r="E106">
         <v>41357</v>
@@ -84156,7 +84156,7 @@
         <v>46144.39685917824</v>
       </c>
       <c r="D107" s="1">
-        <v>46144.646840277775</v>
+        <v>46144.396840277775</v>
       </c>
       <c r="E107">
         <v>40865</v>
@@ -84278,7 +84278,7 @@
         <v>46144.39700869213</v>
       </c>
       <c r="D108" s="1">
-        <v>46144.64697916667</v>
+        <v>46144.39697916667</v>
       </c>
       <c r="E108">
         <v>40541</v>
@@ -84421,7 +84421,7 @@
         <v>46144.397203113425</v>
       </c>
       <c r="D109" s="1">
-        <v>46144.6471875</v>
+        <v>46144.3971875</v>
       </c>
       <c r="E109">
         <v>40054</v>
@@ -84543,7 +84543,7 @@
         <v>46144.39738388889</v>
       </c>
       <c r="D110" s="1">
-        <v>46144.64732638889</v>
+        <v>46144.39732638889</v>
       </c>
       <c r="E110">
         <v>39739</v>
@@ -84686,7 +84686,7 @@
         <v>46144.397550567126</v>
       </c>
       <c r="D111" s="1">
-        <v>46144.64753472222</v>
+        <v>46144.39753472222</v>
       </c>
       <c r="E111">
         <v>39247</v>
@@ -84808,7 +84808,7 @@
         <v>46144.3975905787</v>
       </c>
       <c r="D112" s="1">
-        <v>46144.647569444445</v>
+        <v>46144.397569444445</v>
       </c>
       <c r="E112">
         <v>39207</v>
@@ -84951,7 +84951,7 @@
         <v>46144.397702476854</v>
       </c>
       <c r="D113" s="1">
-        <v>46144.647673611114</v>
+        <v>46144.397673611114</v>
       </c>
       <c r="E113">
         <v>38935</v>
@@ -85094,7 +85094,7 @@
         <v>46144.397897766205</v>
       </c>
       <c r="D114" s="1">
-        <v>46144.647881944446</v>
+        <v>46144.397881944446</v>
       </c>
       <c r="E114">
         <v>38456</v>
@@ -85216,7 +85216,7 @@
         <v>46144.39793677083</v>
       </c>
       <c r="D115" s="1">
-        <v>46144.64791666667</v>
+        <v>46144.39791666667</v>
       </c>
       <c r="E115">
         <v>38414</v>
@@ -85359,7 +85359,7 @@
         <v>46144.39807797454</v>
       </c>
       <c r="D116" s="1">
-        <v>46144.64802083333</v>
+        <v>46144.39802083333</v>
       </c>
       <c r="E116">
         <v>38146</v>
@@ -85502,7 +85502,7 @@
         <v>46144.398244895834</v>
       </c>
       <c r="D117" s="1">
-        <v>46144.64822916667</v>
+        <v>46144.39822916667</v>
       </c>
       <c r="E117">
         <v>37669</v>
@@ -85624,7 +85624,7 @@
         <v>46144.398284282404</v>
       </c>
       <c r="D118" s="1">
-        <v>46144.64826388889</v>
+        <v>46144.39826388889</v>
       </c>
       <c r="E118">
         <v>37625</v>
@@ -85767,7 +85767,7 @@
         <v>46144.39839693287</v>
       </c>
       <c r="D119" s="1">
-        <v>46144.648368055554</v>
+        <v>46144.398368055554</v>
       </c>
       <c r="E119">
         <v>37362</v>
@@ -85910,7 +85910,7 @@
         <v>46144.3985921412</v>
       </c>
       <c r="D120" s="1">
-        <v>46144.64857638889</v>
+        <v>46144.39857638889</v>
       </c>
       <c r="E120">
         <v>36888</v>
@@ -86032,7 +86032,7 @@
         <v>46144.39877305555</v>
       </c>
       <c r="D121" s="1">
-        <v>46144.64871527778</v>
+        <v>46144.39871527778</v>
       </c>
       <c r="E121">
         <v>36593</v>
@@ -86175,7 +86175,7 @@
         <v>46144.39893892361</v>
       </c>
       <c r="D122" s="1">
-        <v>46144.64892361111</v>
+        <v>46144.39892361111</v>
       </c>
       <c r="E122">
         <v>36136</v>
@@ -86297,7 +86297,7 @@
         <v>46144.39897913195</v>
       </c>
       <c r="D123" s="1">
-        <v>46144.64895833333</v>
+        <v>46144.39895833333</v>
       </c>
       <c r="E123">
         <v>36104</v>
@@ -86440,7 +86440,7 @@
         <v>46144.39909210648</v>
       </c>
       <c r="D124" s="1">
-        <v>46144.6490625</v>
+        <v>46144.3990625</v>
       </c>
       <c r="E124">
         <v>35861</v>
@@ -86583,7 +86583,7 @@
         <v>46144.39928668981</v>
       </c>
       <c r="D125" s="1">
-        <v>46144.64927083333</v>
+        <v>46144.39927083333</v>
       </c>
       <c r="E125">
         <v>35418</v>
@@ -86705,7 +86705,7 @@
         <v>46144.39932684028</v>
       </c>
       <c r="D126" s="1">
-        <v>46144.649305555555</v>
+        <v>46144.399305555555</v>
       </c>
       <c r="E126">
         <v>35385</v>
@@ -86848,7 +86848,7 @@
         <v>46144.39946693287</v>
       </c>
       <c r="D127" s="1">
-        <v>46144.649409722224</v>
+        <v>46144.399409722224</v>
       </c>
       <c r="E127">
         <v>35145</v>
@@ -86991,7 +86991,7 @@
         <v>46144.39963341435</v>
       </c>
       <c r="D128" s="1">
-        <v>46144.649618055555</v>
+        <v>46144.399618055555</v>
       </c>
       <c r="E128">
         <v>34709</v>
@@ -87113,7 +87113,7 @@
         <v>46144.39967326389</v>
       </c>
       <c r="D129" s="1">
-        <v>46144.64965277778</v>
+        <v>46144.39965277778</v>
       </c>
       <c r="E129">
         <v>34678</v>
@@ -87256,7 +87256,7 @@
         <v>46144.399786608796</v>
       </c>
       <c r="D130" s="1">
-        <v>46144.64975694445</v>
+        <v>46144.39975694445</v>
       </c>
       <c r="E130">
         <v>34442</v>
@@ -87399,7 +87399,7 @@
         <v>46144.39998173611</v>
       </c>
       <c r="D131" s="1">
-        <v>46144.64996527778</v>
+        <v>46144.39996527778</v>
       </c>
       <c r="E131">
         <v>34013</v>
@@ -87521,7 +87521,7 @@
         <v>46144.400020960646</v>
       </c>
       <c r="D132" s="1">
-        <v>46144.65</v>
+        <v>46144.4</v>
       </c>
       <c r="E132">
         <v>33988</v>
@@ -87664,7 +87664,7 @@
         <v>46144.400161875</v>
       </c>
       <c r="D133" s="1">
-        <v>46144.65010416666</v>
+        <v>46144.40010416666</v>
       </c>
       <c r="E133">
         <v>33751</v>
@@ -87807,7 +87807,7 @@
         <v>46144.400329027776</v>
       </c>
       <c r="D134" s="1">
-        <v>46144.6503125</v>
+        <v>46144.4003125</v>
       </c>
       <c r="E134">
         <v>33334</v>
@@ -87929,7 +87929,7 @@
         <v>46144.40036827546</v>
       </c>
       <c r="D135" s="1">
-        <v>46144.650347222225</v>
+        <v>46144.400347222225</v>
       </c>
       <c r="E135">
         <v>33303</v>
@@ -88072,7 +88072,7 @@
         <v>46144.400480902776</v>
       </c>
       <c r="D136" s="1">
-        <v>46144.65045138889</v>
+        <v>46144.40045138889</v>
       </c>
       <c r="E136">
         <v>33071</v>
@@ -88215,7 +88215,7 @@
         <v>46144.40067483796</v>
       </c>
       <c r="D137" s="1">
-        <v>46144.650659722225</v>
+        <v>46144.400659722225</v>
       </c>
       <c r="E137">
         <v>32645</v>
@@ -88337,7 +88337,7 @@
         <v>46144.4008568287</v>
       </c>
       <c r="D138" s="1">
-        <v>46144.65079861111</v>
+        <v>46144.40079861111</v>
       </c>
       <c r="E138">
         <v>32387</v>
@@ -88480,7 +88480,7 @@
         <v>46144.40102226852</v>
       </c>
       <c r="D139" s="1">
-        <v>46144.65100694444</v>
+        <v>46144.40100694444</v>
       </c>
       <c r="E139">
         <v>31963</v>
@@ -88602,7 +88602,7 @@
         <v>46144.40117453704</v>
       </c>
       <c r="D140" s="1">
-        <v>46144.65114583333</v>
+        <v>46144.40114583333</v>
       </c>
       <c r="E140">
         <v>31706</v>
@@ -88745,7 +88745,7 @@
         <v>46144.40137046296</v>
       </c>
       <c r="D141" s="1">
-        <v>46144.651354166665</v>
+        <v>46144.401354166665</v>
       </c>
       <c r="E141">
         <v>31283</v>
@@ -88867,7 +88867,7 @@
         <v>46144.401551145835</v>
       </c>
       <c r="D142" s="1">
-        <v>46144.65149305556</v>
+        <v>46144.40149305556</v>
       </c>
       <c r="E142">
         <v>31021</v>
@@ -89010,7 +89010,7 @@
         <v>46144.40171721065</v>
       </c>
       <c r="D143" s="1">
-        <v>46144.65170138889</v>
+        <v>46144.40170138889</v>
       </c>
       <c r="E143">
         <v>30604</v>
@@ -89132,7 +89132,7 @@
         <v>46144.40175670139</v>
       </c>
       <c r="D144" s="1">
-        <v>46144.65173611111</v>
+        <v>46144.40173611111</v>
       </c>
       <c r="E144">
         <v>30578</v>
@@ -89275,7 +89275,7 @@
         <v>46144.40186975694</v>
       </c>
       <c r="D145" s="1">
-        <v>46144.65184027778</v>
+        <v>46144.40184027778</v>
       </c>
       <c r="E145">
         <v>30347</v>
@@ -89418,7 +89418,7 @@
         <v>46144.40206474537</v>
       </c>
       <c r="D146" s="1">
-        <v>46144.65204861111</v>
+        <v>46144.40204861111</v>
       </c>
       <c r="E146">
         <v>29935</v>
@@ -89540,7 +89540,7 @@
         <v>46144.40210438657</v>
       </c>
       <c r="D147" s="1">
-        <v>46144.652083333334</v>
+        <v>46144.402083333334</v>
       </c>
       <c r="E147">
         <v>29909</v>
@@ -89683,7 +89683,7 @@
         <v>46144.40224559028</v>
       </c>
       <c r="D148" s="1">
-        <v>46144.6521875</v>
+        <v>46144.4021875</v>
       </c>
       <c r="E148">
         <v>29679</v>
@@ -89826,7 +89826,7 @@
         <v>46144.402411724535</v>
       </c>
       <c r="D149" s="1">
-        <v>46144.652395833335</v>
+        <v>46144.402395833335</v>
       </c>
       <c r="E149">
         <v>29269</v>
@@ -89948,7 +89948,7 @@
         <v>46144.4025643287</v>
       </c>
       <c r="D150" s="1">
-        <v>46144.65253472222</v>
+        <v>46144.40253472222</v>
       </c>
       <c r="E150">
         <v>29010</v>
@@ -90091,7 +90091,7 @@
         <v>46144.40275891204</v>
       </c>
       <c r="D151" s="1">
-        <v>46144.65274305556</v>
+        <v>46144.40274305556</v>
       </c>
       <c r="E151">
         <v>28613</v>
@@ -90213,7 +90213,7 @@
         <v>46144.40279814815</v>
       </c>
       <c r="D152" s="1">
-        <v>46144.65277777778</v>
+        <v>46144.40277777778</v>
       </c>
       <c r="E152">
         <v>28587</v>
@@ -90356,7 +90356,7 @@
         <v>46144.4029421875</v>
       </c>
       <c r="D153" s="1">
-        <v>46144.65288194444</v>
+        <v>46144.40288194444</v>
       </c>
       <c r="E153">
         <v>28359</v>
@@ -90499,7 +90499,7 @@
         <v>46144.40310603009</v>
       </c>
       <c r="D154" s="1">
-        <v>46144.65309027778</v>
+        <v>46144.40309027778</v>
       </c>
       <c r="E154">
         <v>27956</v>
@@ -90621,7 +90621,7 @@
         <v>46144.403145289354</v>
       </c>
       <c r="D155" s="1">
-        <v>46144.653125</v>
+        <v>46144.403125</v>
       </c>
       <c r="E155">
         <v>27930</v>
@@ -90764,7 +90764,7 @@
         <v>46144.40325858796</v>
       </c>
       <c r="D156" s="1">
-        <v>46144.653229166666</v>
+        <v>46144.403229166666</v>
       </c>
       <c r="E156">
         <v>27699</v>
@@ -90907,7 +90907,7 @@
         <v>46144.403453680556</v>
       </c>
       <c r="D157" s="1">
-        <v>46144.6534375</v>
+        <v>46144.4034375</v>
       </c>
       <c r="E157">
         <v>27293</v>
@@ -91029,7 +91029,7 @@
         <v>46144.40349587963</v>
       </c>
       <c r="D158" s="1">
-        <v>46144.65347222222</v>
+        <v>46144.40347222222</v>
       </c>
       <c r="E158">
         <v>27273</v>
@@ -91172,7 +91172,7 @@
         <v>46144.403634282404</v>
       </c>
       <c r="D159" s="1">
-        <v>46144.65357638889</v>
+        <v>46144.40357638889</v>
       </c>
       <c r="E159">
         <v>27045</v>
@@ -91315,7 +91315,7 @@
         <v>46144.403800127315</v>
       </c>
       <c r="D160" s="1">
-        <v>46144.65378472222</v>
+        <v>46144.40378472222</v>
       </c>
       <c r="E160">
         <v>26647</v>
@@ -91437,7 +91437,7 @@
         <v>46144.40384021991</v>
       </c>
       <c r="D161" s="1">
-        <v>46144.653819444444</v>
+        <v>46144.403819444444</v>
       </c>
       <c r="E161">
         <v>26627</v>
@@ -91580,7 +91580,7 @@
         <v>46144.40395289352</v>
       </c>
       <c r="D162" s="1">
-        <v>46144.65392361111</v>
+        <v>46144.40392361111</v>
       </c>
       <c r="E162">
         <v>26405</v>
@@ -91723,7 +91723,7 @@
         <v>46144.40414784722</v>
       </c>
       <c r="D163" s="1">
-        <v>46144.654131944444</v>
+        <v>46144.404131944444</v>
       </c>
       <c r="E163">
         <v>26010</v>
@@ -91845,7 +91845,7 @@
         <v>46144.404187569446</v>
       </c>
       <c r="D164" s="1">
-        <v>46144.65416666667</v>
+        <v>46144.40416666667</v>
       </c>
       <c r="E164">
         <v>25994</v>
@@ -91988,7 +91988,7 @@
         <v>46144.40432873843</v>
       </c>
       <c r="D165" s="1">
-        <v>46144.654270833336</v>
+        <v>46144.404270833336</v>
       </c>
       <c r="E165">
         <v>25778</v>
@@ -92131,7 +92131,7 @@
         <v>46144.40449505787</v>
       </c>
       <c r="D166" s="1">
-        <v>46144.65447916667</v>
+        <v>46144.40447916667</v>
       </c>
       <c r="E166">
         <v>25384</v>
@@ -92253,7 +92253,7 @@
         <v>46144.40453412037</v>
       </c>
       <c r="D167" s="1">
-        <v>46144.65451388889</v>
+        <v>46144.40451388889</v>
       </c>
       <c r="E167">
         <v>25358</v>
@@ -92396,7 +92396,7 @@
         <v>46144.40464746528</v>
       </c>
       <c r="D168" s="1">
-        <v>46144.65461805555</v>
+        <v>46144.40461805555</v>
       </c>
       <c r="E168">
         <v>25135</v>
@@ -92539,7 +92539,7 @@
         <v>46144.4048430787</v>
       </c>
       <c r="D169" s="1">
-        <v>46144.65482638889</v>
+        <v>46144.40482638889</v>
       </c>
       <c r="E169">
         <v>24747</v>
@@ -92661,7 +92661,7 @@
         <v>46144.40488137731</v>
       </c>
       <c r="D170" s="1">
-        <v>46144.654861111114</v>
+        <v>46144.404861111114</v>
       </c>
       <c r="E170">
         <v>24722</v>
@@ -92804,7 +92804,7 @@
         <v>46144.405023506944</v>
       </c>
       <c r="D171" s="1">
-        <v>46144.654965277776</v>
+        <v>46144.404965277776</v>
       </c>
       <c r="E171">
         <v>24506</v>
@@ -92947,7 +92947,7 @@
         <v>46144.40518884259</v>
       </c>
       <c r="D172" s="1">
-        <v>46144.655173611114</v>
+        <v>46144.405173611114</v>
       </c>
       <c r="E172">
         <v>24117</v>
@@ -93069,7 +93069,7 @@
         <v>46144.405229375</v>
       </c>
       <c r="D173" s="1">
-        <v>46144.65520833333</v>
+        <v>46144.40520833333</v>
       </c>
       <c r="E173">
         <v>24098</v>
@@ -93212,7 +93212,7 @@
         <v>46144.40534399306</v>
       </c>
       <c r="D174" s="1">
-        <v>46144.6553125</v>
+        <v>46144.4053125</v>
       </c>
       <c r="E174">
         <v>23883</v>
@@ -93355,7 +93355,7 @@
         <v>46144.40554724537</v>
       </c>
       <c r="D175" s="1">
-        <v>46144.65553240741</v>
+        <v>46144.40553240741</v>
       </c>
       <c r="E175">
         <v>23481</v>
@@ -93477,7 +93477,7 @@
         <v>46144.405576087964</v>
       </c>
       <c r="D176" s="1">
-        <v>46144.65555555555</v>
+        <v>46144.40555555555</v>
       </c>
       <c r="E176">
         <v>23484</v>
@@ -93620,7 +93620,7 @@
         <v>46144.40571773148</v>
       </c>
       <c r="D177" s="1">
-        <v>46144.65565972222</v>
+        <v>46144.40565972222</v>
       </c>
       <c r="E177">
         <v>23277</v>
@@ -93763,7 +93763,7 @@
         <v>46144.40589494213</v>
       </c>
       <c r="D178" s="1">
-        <v>46144.65587962963</v>
+        <v>46144.40587962963</v>
       </c>
       <c r="E178">
         <v>22870</v>
@@ -93885,7 +93885,7 @@
         <v>46144.40592319444</v>
       </c>
       <c r="D179" s="1">
-        <v>46144.65590277778</v>
+        <v>46144.40590277778</v>
       </c>
       <c r="E179">
         <v>22876</v>
@@ -94028,7 +94028,7 @@
         <v>46144.406036319444</v>
       </c>
       <c r="D180" s="1">
-        <v>46144.656006944446</v>
+        <v>46144.406006944446</v>
       </c>
       <c r="E180">
         <v>22668</v>
@@ -94171,7 +94171,7 @@
         <v>46144.40624231481</v>
       </c>
       <c r="D181" s="1">
-        <v>46144.656226851854</v>
+        <v>46144.406226851854</v>
       </c>
       <c r="E181">
         <v>22280</v>
@@ -94293,7 +94293,7 @@
         <v>46144.40641243056</v>
       </c>
       <c r="D182" s="1">
-        <v>46144.65635416667</v>
+        <v>46144.40635416667</v>
       </c>
       <c r="E182">
         <v>22078</v>
@@ -94436,7 +94436,7 @@
         <v>46144.406590729166</v>
       </c>
       <c r="D183" s="1">
-        <v>46144.65657407408</v>
+        <v>46144.40657407408</v>
       </c>
       <c r="E183">
         <v>21689</v>
@@ -94558,7 +94558,7 @@
         <v>46144.40673299768</v>
       </c>
       <c r="D184" s="1">
-        <v>46144.656701388885</v>
+        <v>46144.406701388885</v>
       </c>
       <c r="E184">
         <v>21493</v>
@@ -94701,7 +94701,7 @@
         <v>46144.40693612269</v>
       </c>
       <c r="D185" s="1">
-        <v>46144.65692129629</v>
+        <v>46144.40692129629</v>
       </c>
       <c r="E185">
         <v>21115</v>
@@ -94823,7 +94823,7 @@
         <v>46144.4069659838</v>
       </c>
       <c r="D186" s="1">
-        <v>46144.65694444445</v>
+        <v>46144.40694444445</v>
       </c>
       <c r="E186">
         <v>21119</v>
@@ -94966,7 +94966,7 @@
         <v>46144.40710708333</v>
       </c>
       <c r="D187" s="1">
-        <v>46144.65704861111</v>
+        <v>46144.40704861111</v>
       </c>
       <c r="E187">
         <v>20919</v>
@@ -95109,7 +95109,7 @@
         <v>46144.40728496528</v>
       </c>
       <c r="D188" s="1">
-        <v>46144.65726851852</v>
+        <v>46144.40726851852</v>
       </c>
       <c r="E188">
         <v>20544</v>
@@ -95231,7 +95231,7 @@
         <v>46144.40731243056</v>
       </c>
       <c r="D189" s="1">
-        <v>46144.65729166667</v>
+        <v>46144.40729166667</v>
       </c>
       <c r="E189">
         <v>20549</v>
@@ -95374,7 +95374,7 @@
         <v>46144.40742506945</v>
       </c>
       <c r="D190" s="1">
-        <v>46144.65739583333</v>
+        <v>46144.40739583333</v>
       </c>
       <c r="E190">
         <v>20349</v>
@@ -95517,7 +95517,7 @@
         <v>46144.40763270833</v>
       </c>
       <c r="D191" s="1">
-        <v>46144.65761574074</v>
+        <v>46144.40761574074</v>
       </c>
       <c r="E191">
         <v>19980</v>
@@ -95639,7 +95639,7 @@
         <v>46144.407660474535</v>
       </c>
       <c r="D192" s="1">
-        <v>46144.657638888886</v>
+        <v>46144.407638888886</v>
       </c>
       <c r="E192">
         <v>19987</v>
@@ -95782,7 +95782,7 @@
         <v>46144.40780111111</v>
       </c>
       <c r="D193" s="1">
-        <v>46144.657743055555</v>
+        <v>46144.407743055555</v>
       </c>
       <c r="E193">
         <v>19790</v>
@@ -95925,7 +95925,7 @@
         <v>46144.40797960648</v>
       </c>
       <c r="D194" s="1">
-        <v>46144.65796296296</v>
+        <v>46144.40796296296</v>
       </c>
       <c r="E194">
         <v>19418</v>
@@ -96047,7 +96047,7 @@
         <v>46144.4081190625</v>
       </c>
       <c r="D195" s="1">
-        <v>46144.65809027778</v>
+        <v>46144.40809027778</v>
       </c>
       <c r="E195">
         <v>19230</v>
@@ -96190,7 +96190,7 @@
         <v>46144.40832560185</v>
       </c>
       <c r="D196" s="1">
-        <v>46144.65831018519</v>
+        <v>46144.40831018519</v>
       </c>
       <c r="E196">
         <v>18867</v>
@@ -96312,7 +96312,7 @@
         <v>46144.40849524306</v>
       </c>
       <c r="D197" s="1">
-        <v>46144.6584375</v>
+        <v>46144.4084375</v>
       </c>
       <c r="E197">
         <v>18680</v>
@@ -96455,7 +96455,7 @@
         <v>46144.40867445602</v>
       </c>
       <c r="D198" s="1">
-        <v>46144.65865740741</v>
+        <v>46144.40865740741</v>
       </c>
       <c r="E198">
         <v>18316</v>
@@ -96577,7 +96577,7 @@
         <v>46144.408813333335</v>
       </c>
       <c r="D199" s="1">
-        <v>46144.658784722225</v>
+        <v>46144.408784722225</v>
       </c>
       <c r="E199">
         <v>18131</v>
@@ -96720,7 +96720,7 @@
         <v>46144.40902100695</v>
       </c>
       <c r="D200" s="1">
-        <v>46144.659004629626</v>
+        <v>46144.409004629626</v>
       </c>
       <c r="E200">
         <v>17775</v>
@@ -96842,7 +96842,7 @@
         <v>46144.409190081016</v>
       </c>
       <c r="D201" s="1">
-        <v>46144.65913194444</v>
+        <v>46144.40913194444</v>
       </c>
       <c r="E201">
         <v>17593</v>
@@ -96985,7 +96985,7 @@
         <v>46144.409367314816</v>
       </c>
       <c r="D202" s="1">
-        <v>46144.65935185185</v>
+        <v>46144.40935185185</v>
       </c>
       <c r="E202">
         <v>17230</v>
@@ -97107,7 +97107,7 @@
         <v>46144.40951063657</v>
       </c>
       <c r="D203" s="1">
-        <v>46144.659479166665</v>
+        <v>46144.409479166665</v>
       </c>
       <c r="E203">
         <v>17053</v>
@@ -97250,7 +97250,7 @@
         <v>46144.409726412036</v>
       </c>
       <c r="D204" s="1">
-        <v>46144.65971064815</v>
+        <v>46144.40971064815</v>
       </c>
       <c r="E204">
         <v>16682</v>
@@ -97372,7 +97372,7 @@
         <v>46144.40991350694</v>
       </c>
       <c r="D205" s="1">
-        <v>46144.65972222222</v>
+        <v>46144.40972222222</v>
       </c>
       <c r="E205">
         <v>16706</v>
@@ -97515,7 +97515,7 @@
         <v>46144.40988475695</v>
       </c>
       <c r="D206" s="1">
-        <v>46144.65982638889</v>
+        <v>46144.40982638889</v>
       </c>
       <c r="E206">
         <v>16521</v>
@@ -97658,7 +97658,7 @@
         <v>46144.41007537037</v>
       </c>
       <c r="D207" s="1">
-        <v>46144.66005787037</v>
+        <v>46144.41005787037</v>
       </c>
       <c r="E207">
         <v>16144</v>
@@ -97780,7 +97780,7 @@
         <v>46144.41009048611</v>
       </c>
       <c r="D208" s="1">
-        <v>46144.66006944444</v>
+        <v>46144.41006944444</v>
       </c>
       <c r="E208">
         <v>16176</v>
@@ -97923,7 +97923,7 @@
         <v>46144.41020293981</v>
       </c>
       <c r="D209" s="1">
-        <v>46144.66017361111</v>
+        <v>46144.41017361111</v>
       </c>
       <c r="E209">
         <v>15990</v>
@@ -98066,7 +98066,7 @@
         <v>46144.41042590278</v>
       </c>
       <c r="D210" s="1">
-        <v>46144.660405092596</v>
+        <v>46144.410405092596</v>
       </c>
       <c r="E210">
         <v>15619</v>
@@ -98188,7 +98188,7 @@
         <v>46144.4104371412</v>
       </c>
       <c r="D211" s="1">
-        <v>46144.660416666666</v>
+        <v>46144.410416666666</v>
       </c>
       <c r="E211">
         <v>15645</v>
@@ -98331,7 +98331,7 @@
         <v>46144.41057910879</v>
       </c>
       <c r="D212" s="1">
-        <v>46144.660520833335</v>
+        <v>46144.410520833335</v>
       </c>
       <c r="E212">
         <v>15461</v>
@@ -98474,7 +98474,7 @@
         <v>46144.410768078706</v>
       </c>
       <c r="D213" s="1">
-        <v>46144.66075231481</v>
+        <v>46144.41075231481</v>
       </c>
       <c r="E213">
         <v>15090</v>
@@ -98596,7 +98596,7 @@
         <v>46144.41089824074</v>
       </c>
       <c r="D214" s="1">
-        <v>46144.66086805556</v>
+        <v>46144.41086805556</v>
       </c>
       <c r="E214">
         <v>14936</v>
@@ -98739,7 +98739,7 @@
         <v>46144.41111525463</v>
       </c>
       <c r="D215" s="1">
-        <v>46144.661099537036</v>
+        <v>46144.411099537036</v>
       </c>
       <c r="E215">
         <v>14572</v>
@@ -98861,7 +98861,7 @@
         <v>46144.41146210648</v>
       </c>
       <c r="D216" s="1">
-        <v>46144.66144675926</v>
+        <v>46144.41144675926</v>
       </c>
       <c r="E216">
         <v>14067</v>
@@ -98983,7 +98983,7 @@
         <v>46144.411478449074</v>
       </c>
       <c r="D217" s="1">
-        <v>46144.661458333336</v>
+        <v>46144.411458333336</v>
       </c>
       <c r="E217">
         <v>14095</v>
@@ -99126,7 +99126,7 @@
         <v>46144.41159170139</v>
       </c>
       <c r="D218" s="1">
-        <v>46144.6615625</v>
+        <v>46144.4115625</v>
       </c>
       <c r="E218">
         <v>13935</v>
@@ -99269,7 +99269,7 @@
         <v>46144.411809756944</v>
       </c>
       <c r="D219" s="1">
-        <v>46144.66179398148</v>
+        <v>46144.41179398148</v>
       </c>
       <c r="E219">
         <v>13552</v>
@@ -99391,7 +99391,7 @@
         <v>46144.411968229164</v>
       </c>
       <c r="D220" s="1">
-        <v>46144.66190972222</v>
+        <v>46144.41190972222</v>
       </c>
       <c r="E220">
         <v>13407</v>
@@ -99534,7 +99534,7 @@
         <v>46144.412158657404</v>
       </c>
       <c r="D221" s="1">
-        <v>46144.662141203706</v>
+        <v>46144.412141203706</v>
       </c>
       <c r="E221">
         <v>13023</v>
@@ -99656,7 +99656,7 @@
         <v>46144.412173310186</v>
       </c>
       <c r="D222" s="1">
-        <v>46144.662152777775</v>
+        <v>46144.412152777775</v>
       </c>
       <c r="E222">
         <v>13054</v>
@@ -99799,7 +99799,7 @@
         <v>46144.412286087965</v>
       </c>
       <c r="D223" s="1">
-        <v>46144.662256944444</v>
+        <v>46144.412256944444</v>
       </c>
       <c r="E223">
         <v>12873</v>
@@ -99942,7 +99942,7 @@
         <v>46144.412505162036</v>
       </c>
       <c r="D224" s="1">
-        <v>46144.66248842593</v>
+        <v>46144.41248842593</v>
       </c>
       <c r="E224">
         <v>12511</v>
@@ -100064,7 +100064,7 @@
         <v>46144.41252041667</v>
       </c>
       <c r="D225" s="1">
-        <v>46144.6625</v>
+        <v>46144.4125</v>
       </c>
       <c r="E225">
         <v>12545</v>
@@ -100207,7 +100207,7 @@
         <v>46144.412663773146</v>
       </c>
       <c r="D226" s="1">
-        <v>46144.66260416667</v>
+        <v>46144.41260416667</v>
       </c>
       <c r="E226">
         <v>12363</v>
@@ -100350,7 +100350,7 @@
         <v>46144.412853587964</v>
       </c>
       <c r="D227" s="1">
-        <v>46144.662835648145</v>
+        <v>46144.412835648145</v>
       </c>
       <c r="E227">
         <v>12016</v>
@@ -100472,7 +100472,7 @@
         <v>46144.412980787034</v>
       </c>
       <c r="D228" s="1">
-        <v>46144.66295138889</v>
+        <v>46144.41295138889</v>
       </c>
       <c r="E228">
         <v>11872</v>
@@ -100615,7 +100615,7 @@
         <v>46144.413360046296</v>
       </c>
       <c r="D229" s="1">
-        <v>46144.663298611114</v>
+        <v>46144.413298611114</v>
       </c>
       <c r="E229">
         <v>11380</v>
@@ -100758,7 +100758,7 @@
         <v>46144.41354559028</v>
       </c>
       <c r="D230" s="1">
-        <v>46144.66353009259</v>
+        <v>46144.41353009259</v>
       </c>
       <c r="E230">
         <v>11035</v>
@@ -100880,7 +100880,7 @@
         <v>46144.41356288194</v>
       </c>
       <c r="D231" s="1">
-        <v>46144.66354166667</v>
+        <v>46144.41354166667</v>
       </c>
       <c r="E231">
         <v>11066</v>
@@ -101023,7 +101023,7 @@
         <v>46144.413675497686</v>
       </c>
       <c r="D232" s="1">
-        <v>46144.66364583333</v>
+        <v>46144.41364583333</v>
       </c>
       <c r="E232">
         <v>10900</v>
@@ -101166,7 +101166,7 @@
         <v>46144.41389334491</v>
       </c>
       <c r="D233" s="1">
-        <v>46144.663877314815</v>
+        <v>46144.413877314815</v>
       </c>
       <c r="E233">
         <v>10559</v>
@@ -101288,7 +101288,7 @@
         <v>46144.41405189815</v>
       </c>
       <c r="D234" s="1">
-        <v>46144.663993055554</v>
+        <v>46144.413993055554</v>
       </c>
       <c r="E234">
         <v>10402</v>
@@ -101431,7 +101431,7 @@
         <v>46144.41424081018</v>
       </c>
       <c r="D235" s="1">
-        <v>46144.66422453704</v>
+        <v>46144.41422453704</v>
       </c>
       <c r="E235">
         <v>10050</v>
@@ -101553,7 +101553,7 @@
         <v>46144.41436969907</v>
       </c>
       <c r="D236" s="1">
-        <v>46144.66434027778</v>
+        <v>46144.41434027778</v>
       </c>
       <c r="E236">
         <v>9903</v>
@@ -101696,7 +101696,7 @@
         <v>46144.41458670139</v>
       </c>
       <c r="D237" s="1">
-        <v>46144.66457175926</v>
+        <v>46144.41457175926</v>
       </c>
       <c r="E237">
         <v>9535</v>
@@ -101818,7 +101818,7 @@
         <v>46144.414746180555</v>
       </c>
       <c r="D238" s="1">
-        <v>46144.6646875</v>
+        <v>46144.4146875</v>
       </c>
       <c r="E238">
         <v>9380</v>
